--- a/reports/telegram/aegis_daily_2026-08-07.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-07.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AX$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AW$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX57"/>
+  <dimension ref="A1:AW82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,7 @@
     <col width="10" customWidth="1" min="18" max="18"/>
     <col width="50" customWidth="1" min="19" max="19"/>
     <col width="60" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="44" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -482,12 +482,11 @@
     <col width="15" customWidth="1" min="42" max="42"/>
     <col width="12" customWidth="1" min="43" max="43"/>
     <col width="11" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
-    <col width="32" customWidth="1" min="46" max="46"/>
-    <col width="20" customWidth="1" min="47" max="47"/>
-    <col width="18" customWidth="1" min="48" max="48"/>
-    <col width="17" customWidth="1" min="49" max="49"/>
-    <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="32" customWidth="1" min="45" max="45"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="18" customWidth="1" min="47" max="47"/>
+    <col width="17" customWidth="1" min="48" max="48"/>
+    <col width="20" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -593,7 +592,7 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Alerts</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -713,30 +712,25 @@
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>Lifecycle State</t>
+          <t>Top Drivers</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>Top Drivers</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Portfolio Weight %</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>Portfolio Weight %</t>
+          <t>Expected Alpha %</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Alpha %</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
@@ -760,7 +754,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>R2_NEW</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -800,14 +794,14 @@
         </is>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>31.3</v>
+        <v>33.3</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
@@ -848,7 +842,7 @@
         <v>553.3</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>553.3</v>
+        <v>553.2999877929688</v>
       </c>
       <c r="AF2" s="3" t="n">
         <v>547.77</v>
@@ -883,32 +877,23 @@
       <c r="AP2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AQ2" s="3" t="n">
+      <c r="AQ2" s="3" t="inlineStr"/>
+      <c r="AR2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>Value · Growth · Ai Hybrid</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AU2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>Value · Growth · Ai Hybrid</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr"/>
-      <c r="AV2" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -978,14 +963,14 @@
         </is>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>36.6</v>
+        <v>38.6</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
@@ -1069,24 +1054,19 @@
       </c>
       <c r="AS3" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
           <t>Quality · Mean Reversion · Ai Hybrid</t>
         </is>
       </c>
-      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV3" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -1152,14 +1132,14 @@
         </is>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>43.6</v>
+        <v>45.6</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -1236,31 +1216,26 @@
         <v>2.63</v>
       </c>
       <c r="AQ4" s="3" t="n">
-        <v>2.63</v>
+        <v>1.51</v>
       </c>
       <c r="AR4" s="3" t="n">
         <v>-3.08</v>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
           <t>Quality · Growth · Momentum</t>
         </is>
       </c>
-      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="AV4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AX4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1282,7 @@
         </is>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>4</v>
@@ -1328,14 +1303,14 @@
         </is>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>32.2</v>
+        <v>34.2</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
@@ -1376,7 +1351,7 @@
         <v>853.4</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>853.4</v>
+        <v>853.4000244140625</v>
       </c>
       <c r="AF5" s="3" t="n">
         <v>844.87</v>
@@ -1409,32 +1384,23 @@
         <v>0.99</v>
       </c>
       <c r="AP5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
           <t>Value · Mean Reversion · Ai Hybrid</t>
         </is>
       </c>
+      <c r="AT5" s="3" t="inlineStr"/>
       <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="n">
+      <c r="AV5" s="3" t="n">
         <v>7.39</v>
       </c>
-      <c r="AX5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -1510,19 +1476,19 @@
         </is>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>40.4</v>
+        <v>42.4</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank ↑ 8→5 · Conf 43% · band HOLD→STRONG · 16d left · → EXIT (rotate to GNFC.NS)</t>
+          <t>🔴 AVOID · Rank ↑ 8→5 · Conf 43% · band STRONG · 16d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr"/>
@@ -1601,22 +1567,17 @@
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
           <t>Quality · Trend · Mean Reversion</t>
         </is>
       </c>
+      <c r="AT6" s="3" t="inlineStr"/>
       <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="n">
+      <c r="AV6" s="3" t="n">
         <v>7.79</v>
       </c>
-      <c r="AX6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -1684,14 +1645,14 @@
         </is>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>32.5</v>
+        <v>34.5</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1767,30 +1728,21 @@
       <c r="AP7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AQ7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr"/>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
           <t>Trend · Growth · Mean Reversion</t>
         </is>
       </c>
+      <c r="AT7" s="3" t="inlineStr"/>
       <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="n">
+      <c r="AV7" s="3" t="n">
         <v>7.97</v>
       </c>
-      <c r="AX7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -1858,14 +1810,14 @@
         </is>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -1942,29 +1894,24 @@
         <v>0.65</v>
       </c>
       <c r="AQ8" s="3" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="AR8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
           <t>Mean Reversion · Value · Ai Hybrid</t>
         </is>
       </c>
+      <c r="AT8" s="3" t="inlineStr"/>
       <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="n">
+      <c r="AV8" s="3" t="n">
         <v>10.34</v>
       </c>
-      <c r="AX8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -2040,19 +1987,19 @@
         </is>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>35.6</v>
+        <v>37.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank ↓ 2→8 · Conf 38% · band HOLD→STRONG · 16d left · → EXIT (rotate to GNFC.NS)</t>
+          <t>🔴 AVOID · Rank ↓ 2→8 · Conf 38% · band STRONG · 16d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr"/>
@@ -2124,29 +2071,24 @@
         <v>8.75</v>
       </c>
       <c r="AQ9" s="3" t="n">
-        <v>8.75</v>
+        <v>6.76</v>
       </c>
       <c r="AR9" s="3" t="n">
         <v>-0.91</v>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
           <t>Trend · Quality · Growth</t>
         </is>
       </c>
+      <c r="AT9" s="3" t="inlineStr"/>
       <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="n">
+      <c r="AV9" s="3" t="n">
         <v>10.59</v>
       </c>
-      <c r="AX9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -2222,14 +2164,14 @@
         </is>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>30.6</v>
+        <v>32.6</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2306,29 +2248,24 @@
         <v>5.81</v>
       </c>
       <c r="AQ10" s="3" t="n">
-        <v>5.81</v>
+        <v>0.38</v>
       </c>
       <c r="AR10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
           <t>Mean Reversion · Value · Growth</t>
         </is>
       </c>
+      <c r="AT10" s="3" t="inlineStr"/>
       <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="n">
+      <c r="AV10" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="AX10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -2400,14 +2337,14 @@
         </is>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2484,29 +2421,24 @@
         <v>1.85</v>
       </c>
       <c r="AQ11" s="3" t="n">
-        <v>1.85</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" s="3" t="n">
         <v>-3.51</v>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT11" s="3" t="inlineStr">
-        <is>
           <t>Mean Reversion · Quality · Momentum</t>
         </is>
       </c>
+      <c r="AT11" s="3" t="inlineStr"/>
       <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="n">
+      <c r="AV11" s="3" t="n">
         <v>11.69</v>
       </c>
-      <c r="AX11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -2578,14 +2510,14 @@
         </is>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>27.2</v>
+        <v>29.2</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
@@ -2669,22 +2601,17 @@
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
         </is>
       </c>
+      <c r="AT12" s="3" t="inlineStr"/>
       <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="inlineStr"/>
-      <c r="AW12" s="3" t="n">
+      <c r="AV12" s="3" t="n">
         <v>59.69</v>
       </c>
-      <c r="AX12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -2760,14 +2687,14 @@
         </is>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>27.2</v>
+        <v>29.2</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
@@ -2851,22 +2778,17 @@
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
         </is>
       </c>
+      <c r="AT13" s="3" t="inlineStr"/>
       <c r="AU13" s="3" t="inlineStr"/>
-      <c r="AV13" s="3" t="inlineStr"/>
-      <c r="AW13" s="3" t="n">
+      <c r="AV13" s="3" t="n">
         <v>59.88</v>
       </c>
-      <c r="AX13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2810,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>R2_NEW</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2913,7 +2835,7 @@
         </is>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>13</v>
@@ -2934,14 +2856,14 @@
         </is>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>22.1</v>
+        <v>24.1</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -2982,7 +2904,7 @@
         <v>471.2</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>471.2</v>
+        <v>471.2000122070312</v>
       </c>
       <c r="AF14" s="3" t="n">
         <v>466.49</v>
@@ -3015,32 +2937,23 @@
         <v>-2.24</v>
       </c>
       <c r="AP14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr"/>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
         </is>
       </c>
+      <c r="AT14" s="3" t="inlineStr"/>
       <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="n">
+      <c r="AV14" s="3" t="n">
         <v>60.67</v>
       </c>
-      <c r="AX14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -3108,14 +3021,14 @@
         </is>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>22.1</v>
+        <v>24.1</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -3191,30 +3104,21 @@
       <c r="AP15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AQ15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr"/>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Distance From 52W High Pct · Distance From 52W Low Pct · Earn Days To Next</t>
         </is>
       </c>
+      <c r="AT15" s="3" t="inlineStr"/>
       <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="inlineStr"/>
-      <c r="AW15" s="3" t="n">
+      <c r="AV15" s="3" t="n">
         <v>62.51</v>
       </c>
-      <c r="AX15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -3282,14 +3186,14 @@
         </is>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>21.3</v>
+        <v>23.3</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>overall breadth 23.3% → -2.0pts · crude +19.8% (rising) → +1.0pts</t>
+          <t>crude +19.8% (rising) → +1.0pts</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -3369,26 +3273,21 @@
         <v>0</v>
       </c>
       <c r="AR16" s="3" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Distance From 52W High Pct</t>
         </is>
       </c>
+      <c r="AT16" s="3" t="inlineStr"/>
       <c r="AU16" s="3" t="inlineStr"/>
-      <c r="AV16" s="3" t="inlineStr"/>
-      <c r="AW16" s="3" t="n">
+      <c r="AV16" s="3" t="n">
         <v>64.81999999999999</v>
       </c>
-      <c r="AX16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -3523,26 +3422,21 @@
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr"/>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr"/>
-      <c r="AU17" s="3" t="inlineStr">
+      <c r="AS17" s="3" t="inlineStr"/>
+      <c r="AT17" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
+      <c r="AU17" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV17" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW17" s="3" t="n">
         <v>5.34</v>
       </c>
-      <c r="AX17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -3677,26 +3571,21 @@
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr"/>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr"/>
-      <c r="AU18" s="3" t="inlineStr">
+      <c r="AS18" s="3" t="inlineStr"/>
+      <c r="AT18" s="3" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
+      <c r="AU18" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV18" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW18" s="3" t="n">
         <v>4.57</v>
       </c>
-      <c r="AX18" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -3835,26 +3724,21 @@
       <c r="AR19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT19" s="3" t="inlineStr"/>
-      <c r="AU19" s="3" t="inlineStr">
+      <c r="AS19" s="3" t="inlineStr"/>
+      <c r="AT19" s="3" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
+      <c r="AU19" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV19" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW19" s="3" t="n">
         <v>5.66</v>
       </c>
-      <c r="AX19" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -3989,26 +3873,21 @@
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr"/>
-      <c r="AS20" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT20" s="3" t="inlineStr"/>
-      <c r="AU20" s="3" t="inlineStr">
+      <c r="AS20" s="3" t="inlineStr"/>
+      <c r="AT20" s="3" t="inlineStr">
         <is>
           <t>Chemicals</t>
         </is>
       </c>
+      <c r="AU20" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV20" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW20" s="3" t="n">
         <v>1.39</v>
       </c>
-      <c r="AX20" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -4143,26 +4022,21 @@
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr"/>
-      <c r="AS21" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT21" s="3" t="inlineStr"/>
-      <c r="AU21" s="3" t="inlineStr">
+      <c r="AS21" s="3" t="inlineStr"/>
+      <c r="AT21" s="3" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
+      <c r="AU21" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV21" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX21" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -4297,26 +4171,21 @@
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr"/>
-      <c r="AS22" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT22" s="3" t="inlineStr"/>
-      <c r="AU22" s="3" t="inlineStr">
+      <c r="AS22" s="3" t="inlineStr"/>
+      <c r="AT22" s="3" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
+      <c r="AU22" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV22" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW22" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX22" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -4451,26 +4320,21 @@
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr"/>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr"/>
-      <c r="AU23" s="3" t="inlineStr">
+      <c r="AS23" s="3" t="inlineStr"/>
+      <c r="AT23" s="3" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
+      <c r="AU23" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV23" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW23" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -4605,26 +4469,21 @@
       <c r="AR24" s="3" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AS24" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT24" s="3" t="inlineStr"/>
-      <c r="AU24" s="3" t="inlineStr">
+      <c r="AS24" s="3" t="inlineStr"/>
+      <c r="AT24" s="3" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
+      <c r="AU24" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV24" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW24" s="3" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AX24" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -4759,26 +4618,21 @@
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr"/>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT25" s="3" t="inlineStr"/>
-      <c r="AU25" s="3" t="inlineStr">
+      <c r="AS25" s="3" t="inlineStr"/>
+      <c r="AT25" s="3" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
+      <c r="AU25" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV25" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW25" s="3" t="n">
         <v>8.01</v>
       </c>
-      <c r="AX25" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -4913,26 +4767,21 @@
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr"/>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr"/>
-      <c r="AU26" s="3" t="inlineStr">
+      <c r="AS26" s="3" t="inlineStr"/>
+      <c r="AT26" s="3" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
+      <c r="AU26" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV26" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW26" s="3" t="n">
         <v>7.99</v>
       </c>
-      <c r="AX26" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -5071,26 +4920,21 @@
       <c r="AR27" s="3" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AS27" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT27" s="3" t="inlineStr"/>
-      <c r="AU27" s="3" t="inlineStr">
+      <c r="AS27" s="3" t="inlineStr"/>
+      <c r="AT27" s="3" t="inlineStr">
         <is>
           <t>Metal</t>
         </is>
       </c>
+      <c r="AU27" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV27" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW27" s="3" t="n">
         <v>8.92</v>
       </c>
-      <c r="AX27" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -5221,26 +5065,21 @@
       </c>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr"/>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr"/>
-      <c r="AU28" s="3" t="inlineStr">
+      <c r="AS28" s="3" t="inlineStr"/>
+      <c r="AT28" s="3" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
+      <c r="AU28" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AV28" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW28" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX28" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -5379,20 +5218,15 @@
       <c r="AR29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS29" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS29" s="3" t="inlineStr"/>
       <c r="AT29" s="3" t="inlineStr"/>
       <c r="AU29" s="3" t="inlineStr"/>
-      <c r="AV29" s="3" t="inlineStr"/>
-      <c r="AW29" s="3" t="n">
+      <c r="AV29" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX29" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -5527,20 +5361,15 @@
       <c r="AR30" s="3" t="n">
         <v>-1.34</v>
       </c>
-      <c r="AS30" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS30" s="3" t="inlineStr"/>
       <c r="AT30" s="3" t="inlineStr"/>
       <c r="AU30" s="3" t="inlineStr"/>
-      <c r="AV30" s="3" t="inlineStr"/>
-      <c r="AW30" s="3" t="n">
+      <c r="AV30" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX30" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -5675,20 +5504,15 @@
       <c r="AR31" s="3" t="n">
         <v>-0.32</v>
       </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS31" s="3" t="inlineStr"/>
       <c r="AT31" s="3" t="inlineStr"/>
       <c r="AU31" s="3" t="inlineStr"/>
-      <c r="AV31" s="3" t="inlineStr"/>
-      <c r="AW31" s="3" t="n">
+      <c r="AV31" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX31" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -5827,20 +5651,15 @@
       <c r="AR32" s="3" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS32" s="3" t="inlineStr"/>
       <c r="AT32" s="3" t="inlineStr"/>
       <c r="AU32" s="3" t="inlineStr"/>
-      <c r="AV32" s="3" t="inlineStr"/>
-      <c r="AW32" s="3" t="n">
+      <c r="AV32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX32" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -5975,20 +5794,15 @@
       <c r="AR33" s="3" t="n">
         <v>-1.5</v>
       </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS33" s="3" t="inlineStr"/>
       <c r="AT33" s="3" t="inlineStr"/>
       <c r="AU33" s="3" t="inlineStr"/>
-      <c r="AV33" s="3" t="inlineStr"/>
-      <c r="AW33" s="3" t="n">
+      <c r="AV33" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX33" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -6123,20 +5937,15 @@
       <c r="AR34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS34" s="3" t="inlineStr"/>
       <c r="AT34" s="3" t="inlineStr"/>
       <c r="AU34" s="3" t="inlineStr"/>
-      <c r="AV34" s="3" t="inlineStr"/>
-      <c r="AW34" s="3" t="n">
+      <c r="AV34" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX34" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -6271,20 +6080,15 @@
       <c r="AR35" s="3" t="n">
         <v>-2.07</v>
       </c>
-      <c r="AS35" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS35" s="3" t="inlineStr"/>
       <c r="AT35" s="3" t="inlineStr"/>
       <c r="AU35" s="3" t="inlineStr"/>
-      <c r="AV35" s="3" t="inlineStr"/>
-      <c r="AW35" s="3" t="n">
+      <c r="AV35" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX35" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -6419,20 +6223,15 @@
       <c r="AR36" s="3" t="n">
         <v>-0.31</v>
       </c>
-      <c r="AS36" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS36" s="3" t="inlineStr"/>
       <c r="AT36" s="3" t="inlineStr"/>
       <c r="AU36" s="3" t="inlineStr"/>
-      <c r="AV36" s="3" t="inlineStr"/>
-      <c r="AW36" s="3" t="n">
+      <c r="AV36" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX36" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6279,7 @@
       <c r="I37" s="3" t="inlineStr"/>
       <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L37" s="3" t="inlineStr"/>
       <c r="M37" s="3" t="inlineStr"/>
@@ -6492,7 +6291,7 @@
       <c r="S37" s="3" t="inlineStr"/>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-0.7%) · Rank #14 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-0.7%) · Rank #11 · Conf 24% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr"/>
@@ -6505,7 +6304,7 @@
         </is>
       </c>
       <c r="X37" s="3" t="n">
-        <v>-28.1</v>
+        <v>-27</v>
       </c>
       <c r="Y37" s="3" t="inlineStr"/>
       <c r="Z37" s="3" t="n">
@@ -6567,20 +6366,15 @@
       <c r="AR37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS37" s="3" t="inlineStr"/>
       <c r="AT37" s="3" t="inlineStr"/>
       <c r="AU37" s="3" t="inlineStr"/>
-      <c r="AV37" s="3" t="inlineStr"/>
-      <c r="AW37" s="3" t="n">
+      <c r="AV37" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX37" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -6715,20 +6509,15 @@
       <c r="AR38" s="3" t="n">
         <v>-0.24</v>
       </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS38" s="3" t="inlineStr"/>
       <c r="AT38" s="3" t="inlineStr"/>
       <c r="AU38" s="3" t="inlineStr"/>
-      <c r="AV38" s="3" t="inlineStr"/>
-      <c r="AW38" s="3" t="n">
+      <c r="AV38" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX38" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -6859,20 +6648,15 @@
       <c r="AR39" s="3" t="n">
         <v>-4.99</v>
       </c>
-      <c r="AS39" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS39" s="3" t="inlineStr"/>
       <c r="AT39" s="3" t="inlineStr"/>
       <c r="AU39" s="3" t="inlineStr"/>
-      <c r="AV39" s="3" t="inlineStr"/>
-      <c r="AW39" s="3" t="n">
+      <c r="AV39" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX39" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -7003,20 +6787,15 @@
       <c r="AR40" s="3" t="n">
         <v>-2.93</v>
       </c>
-      <c r="AS40" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS40" s="3" t="inlineStr"/>
       <c r="AT40" s="3" t="inlineStr"/>
       <c r="AU40" s="3" t="inlineStr"/>
-      <c r="AV40" s="3" t="inlineStr"/>
-      <c r="AW40" s="3" t="n">
+      <c r="AV40" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX40" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -7147,20 +6926,15 @@
       <c r="AR41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS41" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS41" s="3" t="inlineStr"/>
       <c r="AT41" s="3" t="inlineStr"/>
       <c r="AU41" s="3" t="inlineStr"/>
-      <c r="AV41" s="3" t="inlineStr"/>
-      <c r="AW41" s="3" t="n">
+      <c r="AV41" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX41" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -7291,20 +7065,15 @@
       <c r="AR42" s="3" t="n">
         <v>-0.92</v>
       </c>
-      <c r="AS42" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS42" s="3" t="inlineStr"/>
       <c r="AT42" s="3" t="inlineStr"/>
       <c r="AU42" s="3" t="inlineStr"/>
-      <c r="AV42" s="3" t="inlineStr"/>
-      <c r="AW42" s="3" t="n">
+      <c r="AV42" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX42" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7117,7 @@
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L43" s="3" t="inlineStr"/>
       <c r="M43" s="3" t="inlineStr"/>
@@ -7360,7 +7129,7 @@
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>Rank #7 · Conf 41% · momentum → · 61d left · → HOLD</t>
+          <t>Rank #10 · Conf 41% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr"/>
@@ -7373,7 +7142,7 @@
         </is>
       </c>
       <c r="X43" s="3" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="n">
@@ -7405,18 +7174,13 @@
       <c r="AP43" s="3" t="inlineStr"/>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr"/>
-      <c r="AS43" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS43" s="3" t="inlineStr"/>
       <c r="AT43" s="3" t="inlineStr"/>
       <c r="AU43" s="3" t="inlineStr"/>
       <c r="AV43" s="3" t="inlineStr"/>
-      <c r="AW43" s="3" t="inlineStr"/>
-      <c r="AX43" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -7517,18 +7281,13 @@
       <c r="AP44" s="3" t="inlineStr"/>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr"/>
-      <c r="AS44" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS44" s="3" t="inlineStr"/>
       <c r="AT44" s="3" t="inlineStr"/>
       <c r="AU44" s="3" t="inlineStr"/>
       <c r="AV44" s="3" t="inlineStr"/>
-      <c r="AW44" s="3" t="inlineStr"/>
-      <c r="AX44" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -7629,18 +7388,13 @@
       <c r="AP45" s="3" t="inlineStr"/>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr"/>
-      <c r="AS45" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS45" s="3" t="inlineStr"/>
       <c r="AT45" s="3" t="inlineStr"/>
       <c r="AU45" s="3" t="inlineStr"/>
       <c r="AV45" s="3" t="inlineStr"/>
-      <c r="AW45" s="3" t="inlineStr"/>
-      <c r="AX45" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -7749,18 +7503,13 @@
       <c r="AP46" s="3" t="inlineStr"/>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr"/>
-      <c r="AS46" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS46" s="3" t="inlineStr"/>
       <c r="AT46" s="3" t="inlineStr"/>
       <c r="AU46" s="3" t="inlineStr"/>
       <c r="AV46" s="3" t="inlineStr"/>
-      <c r="AW46" s="3" t="inlineStr"/>
-      <c r="AX46" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -7869,18 +7618,13 @@
       <c r="AP47" s="3" t="inlineStr"/>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr"/>
-      <c r="AS47" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS47" s="3" t="inlineStr"/>
       <c r="AT47" s="3" t="inlineStr"/>
       <c r="AU47" s="3" t="inlineStr"/>
       <c r="AV47" s="3" t="inlineStr"/>
-      <c r="AW47" s="3" t="inlineStr"/>
-      <c r="AX47" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -8019,20 +7763,15 @@
       <c r="AR48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AS48" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS48" s="3" t="inlineStr"/>
       <c r="AT48" s="3" t="inlineStr"/>
       <c r="AU48" s="3" t="inlineStr"/>
-      <c r="AV48" s="3" t="inlineStr"/>
-      <c r="AW48" s="3" t="n">
+      <c r="AV48" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX48" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -8141,18 +7880,13 @@
       <c r="AP49" s="3" t="inlineStr"/>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr"/>
-      <c r="AS49" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS49" s="3" t="inlineStr"/>
       <c r="AT49" s="3" t="inlineStr"/>
       <c r="AU49" s="3" t="inlineStr"/>
       <c r="AV49" s="3" t="inlineStr"/>
-      <c r="AW49" s="3" t="inlineStr"/>
-      <c r="AX49" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -8261,18 +7995,13 @@
       <c r="AP50" s="3" t="inlineStr"/>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr"/>
-      <c r="AS50" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS50" s="3" t="inlineStr"/>
       <c r="AT50" s="3" t="inlineStr"/>
       <c r="AU50" s="3" t="inlineStr"/>
       <c r="AV50" s="3" t="inlineStr"/>
-      <c r="AW50" s="3" t="inlineStr"/>
-      <c r="AX50" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -8381,18 +8110,13 @@
       <c r="AP51" s="3" t="inlineStr"/>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr"/>
-      <c r="AS51" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS51" s="3" t="inlineStr"/>
       <c r="AT51" s="3" t="inlineStr"/>
       <c r="AU51" s="3" t="inlineStr"/>
       <c r="AV51" s="3" t="inlineStr"/>
-      <c r="AW51" s="3" t="inlineStr"/>
-      <c r="AX51" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -8501,18 +8225,13 @@
       <c r="AP52" s="3" t="inlineStr"/>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr"/>
-      <c r="AS52" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS52" s="3" t="inlineStr"/>
       <c r="AT52" s="3" t="inlineStr"/>
       <c r="AU52" s="3" t="inlineStr"/>
       <c r="AV52" s="3" t="inlineStr"/>
-      <c r="AW52" s="3" t="inlineStr"/>
-      <c r="AX52" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -8621,18 +8340,13 @@
       <c r="AP53" s="3" t="inlineStr"/>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr"/>
-      <c r="AS53" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS53" s="3" t="inlineStr"/>
       <c r="AT53" s="3" t="inlineStr"/>
       <c r="AU53" s="3" t="inlineStr"/>
       <c r="AV53" s="3" t="inlineStr"/>
-      <c r="AW53" s="3" t="inlineStr"/>
-      <c r="AX53" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -8741,18 +8455,13 @@
       <c r="AP54" s="3" t="inlineStr"/>
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr"/>
-      <c r="AS54" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS54" s="3" t="inlineStr"/>
       <c r="AT54" s="3" t="inlineStr"/>
       <c r="AU54" s="3" t="inlineStr"/>
       <c r="AV54" s="3" t="inlineStr"/>
-      <c r="AW54" s="3" t="inlineStr"/>
-      <c r="AX54" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -8891,20 +8600,15 @@
       <c r="AR55" s="3" t="n">
         <v>-0.11</v>
       </c>
-      <c r="AS55" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS55" s="3" t="inlineStr"/>
       <c r="AT55" s="3" t="inlineStr"/>
       <c r="AU55" s="3" t="inlineStr"/>
-      <c r="AV55" s="3" t="inlineStr"/>
-      <c r="AW55" s="3" t="n">
+      <c r="AV55" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AX55" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -9009,18 +8713,13 @@
       <c r="AP56" s="3" t="inlineStr"/>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr"/>
-      <c r="AS56" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS56" s="3" t="inlineStr"/>
       <c r="AT56" s="3" t="inlineStr"/>
       <c r="AU56" s="3" t="inlineStr"/>
       <c r="AV56" s="3" t="inlineStr"/>
-      <c r="AW56" s="3" t="inlineStr"/>
-      <c r="AX56" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
@@ -9129,23 +8828,4377 @@
       <c r="AP57" s="3" t="inlineStr"/>
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr"/>
-      <c r="AS57" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="AS57" s="3" t="inlineStr"/>
       <c r="AT57" s="3" t="inlineStr"/>
       <c r="AU57" s="3" t="inlineStr"/>
       <c r="AV57" s="3" t="inlineStr"/>
-      <c r="AW57" s="3" t="inlineStr"/>
-      <c r="AX57" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 03:31</t>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>TRV_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr"/>
+      <c r="K58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S58" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T58" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.2% ≤ -5% · exit</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="Y58" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z58" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA58" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB58" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="AE58" s="3" t="n">
+        <v>389.01</v>
+      </c>
+      <c r="AF58" s="3" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="AG58" s="3" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="AH58" s="3" t="n">
+        <v>346.84</v>
+      </c>
+      <c r="AI58" s="3" t="n">
+        <v>-10.84</v>
+      </c>
+      <c r="AJ58" s="3" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AK58" s="3" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="AL58" s="3" t="n">
+        <v>457.54</v>
+      </c>
+      <c r="AM58" s="3" t="n">
+        <v>17.62</v>
+      </c>
+      <c r="AN58" s="3" t="n">
+        <v>377.15</v>
+      </c>
+      <c r="AO58" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AP58" s="3" t="n">
+        <v>-5.15</v>
+      </c>
+      <c r="AQ58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR58" s="3" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Trend</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr"/>
+      <c r="AU58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV58" s="3" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>V_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr"/>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S59" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T59" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.7%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U59" s="3" t="inlineStr"/>
+      <c r="V59" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="Y59" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z59" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA59" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB59" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="AE59" s="3" t="n">
+        <v>368.73</v>
+      </c>
+      <c r="AF59" s="3" t="n">
+        <v>365.04</v>
+      </c>
+      <c r="AG59" s="3" t="n">
+        <v>372.42</v>
+      </c>
+      <c r="AH59" s="3" t="n">
+        <v>350.29</v>
+      </c>
+      <c r="AI59" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ59" s="3" t="n">
+        <v>398.23</v>
+      </c>
+      <c r="AK59" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL59" s="3" t="n">
+        <v>424.04</v>
+      </c>
+      <c r="AM59" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN59" s="3" t="n">
+        <v>369.59</v>
+      </c>
+      <c r="AO59" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AP59" s="3" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="AQ59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR59" s="3" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>Momentum · Trend · Quality</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr"/>
+      <c r="AU59" s="3" t="inlineStr"/>
+      <c r="AV59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>NVDA_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +12.2pp alpha</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S60" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T60" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 3→3 · Conf 47% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="U60" s="3" t="inlineStr"/>
+      <c r="V60" s="3" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y60" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z60" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA60" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB60" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="AE60" s="3" t="n">
+        <v>190.01</v>
+      </c>
+      <c r="AF60" s="3" t="n">
+        <v>188.11</v>
+      </c>
+      <c r="AG60" s="3" t="n">
+        <v>191.91</v>
+      </c>
+      <c r="AH60" s="3" t="n">
+        <v>180.51</v>
+      </c>
+      <c r="AI60" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ60" s="3" t="n">
+        <v>205.21</v>
+      </c>
+      <c r="AK60" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL60" s="3" t="n">
+        <v>218.51</v>
+      </c>
+      <c r="AM60" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN60" s="3" t="n">
+        <v>211.94</v>
+      </c>
+      <c r="AO60" s="3" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AP60" s="3" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="AQ60" s="3" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AR60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>Quality · Growth · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr"/>
+      <c r="AU60" s="3" t="inlineStr"/>
+      <c r="AV60" s="3" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>JPM_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +13.0pp alpha</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S61" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T61" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 4→4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="U61" s="3" t="inlineStr"/>
+      <c r="V61" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="Y61" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z61" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA61" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB61" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC61" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD61" s="3" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="AE61" s="3" t="n">
+        <v>344.71</v>
+      </c>
+      <c r="AF61" s="3" t="n">
+        <v>341.26</v>
+      </c>
+      <c r="AG61" s="3" t="n">
+        <v>348.16</v>
+      </c>
+      <c r="AH61" s="3" t="n">
+        <v>327.47</v>
+      </c>
+      <c r="AI61" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ61" s="3" t="n">
+        <v>372.29</v>
+      </c>
+      <c r="AK61" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL61" s="3" t="n">
+        <v>396.42</v>
+      </c>
+      <c r="AM61" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN61" s="3" t="n">
+        <v>357.52</v>
+      </c>
+      <c r="AO61" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AP61" s="3" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="AQ61" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AR61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr"/>
+      <c r="AU61" s="3" t="inlineStr"/>
+      <c r="AV61" s="3" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="AW61" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>HON_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.4pp alpha</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>-6.68</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S62" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T62" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.7% ≤ -5% · exit</t>
+        </is>
+      </c>
+      <c r="V62" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Y62" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z62" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA62" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB62" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC62" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD62" s="3" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="AE62" s="3" t="n">
+        <v>241.12</v>
+      </c>
+      <c r="AF62" s="3" t="n">
+        <v>238.71</v>
+      </c>
+      <c r="AG62" s="3" t="n">
+        <v>243.53</v>
+      </c>
+      <c r="AH62" s="3" t="n">
+        <v>229.06</v>
+      </c>
+      <c r="AI62" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ62" s="3" t="n">
+        <v>260.41</v>
+      </c>
+      <c r="AK62" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL62" s="3" t="n">
+        <v>277.29</v>
+      </c>
+      <c r="AM62" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN62" s="3" t="n">
+        <v>248.79</v>
+      </c>
+      <c r="AO62" s="3" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AP62" s="3" t="n">
+        <v>-6.68</v>
+      </c>
+      <c r="AQ62" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Growth · Value</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr"/>
+      <c r="AU62" s="3" t="inlineStr"/>
+      <c r="AV62" s="3" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>GS_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.8pp alpha</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S63" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T63" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 6→6 · Conf 51% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="U63" s="3" t="inlineStr"/>
+      <c r="V63" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y63" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z63" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA63" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB63" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC63" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD63" s="3" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="AE63" s="3" t="n">
+        <v>980.75</v>
+      </c>
+      <c r="AF63" s="3" t="n">
+        <v>970.9400000000001</v>
+      </c>
+      <c r="AG63" s="3" t="n">
+        <v>990.5599999999999</v>
+      </c>
+      <c r="AH63" s="3" t="n">
+        <v>931.71</v>
+      </c>
+      <c r="AI63" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ63" s="3" t="n">
+        <v>1059.21</v>
+      </c>
+      <c r="AK63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL63" s="3" t="n">
+        <v>1127.86</v>
+      </c>
+      <c r="AM63" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN63" s="3" t="n">
+        <v>1052.98</v>
+      </c>
+      <c r="AO63" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP63" s="3" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="AQ63" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>Value · News · Event Driven</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr"/>
+      <c r="AU63" s="3" t="inlineStr"/>
+      <c r="AV63" s="3" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="AW63" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>AAPL_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.9pp alpha</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S64" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T64" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 7→7 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="U64" s="3" t="inlineStr"/>
+      <c r="V64" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="Y64" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z64" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA64" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB64" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC64" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD64" s="3" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="AE64" s="3" t="n">
+        <v>338.19</v>
+      </c>
+      <c r="AF64" s="3" t="n">
+        <v>334.81</v>
+      </c>
+      <c r="AG64" s="3" t="n">
+        <v>341.57</v>
+      </c>
+      <c r="AH64" s="3" t="n">
+        <v>321.28</v>
+      </c>
+      <c r="AI64" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ64" s="3" t="n">
+        <v>365.25</v>
+      </c>
+      <c r="AK64" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL64" s="3" t="n">
+        <v>388.92</v>
+      </c>
+      <c r="AM64" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN64" s="3" t="n">
+        <v>309.38</v>
+      </c>
+      <c r="AO64" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AP64" s="3" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="AQ64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR64" s="3" t="n">
+        <v>-8.66</v>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>Value · Trend · Momentum</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr"/>
+      <c r="AU64" s="3" t="inlineStr"/>
+      <c r="AV64" s="3" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="AW64" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>MSFT_USA_20260730</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +15.2pp alpha</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="M65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S65" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T65" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="U65" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-12.7% ≤ -8% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y65" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z65" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA65" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB65" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AC65" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD65" s="3" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="AE65" s="3" t="n">
+        <v>451.1</v>
+      </c>
+      <c r="AF65" s="3" t="n">
+        <v>446.59</v>
+      </c>
+      <c r="AG65" s="3" t="n">
+        <v>455.61</v>
+      </c>
+      <c r="AH65" s="3" t="n">
+        <v>428.55</v>
+      </c>
+      <c r="AI65" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ65" s="3" t="n">
+        <v>487.19</v>
+      </c>
+      <c r="AK65" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL65" s="3" t="n">
+        <v>518.76</v>
+      </c>
+      <c r="AM65" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN65" s="3" t="n">
+        <v>492.81</v>
+      </c>
+      <c r="AO65" s="3" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AP65" s="3" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="AQ65" s="3" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AR65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>Quality · Mean Reversion · Trend</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr"/>
+      <c r="AU65" s="3" t="inlineStr"/>
+      <c r="AV65" s="3" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>KO_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +15.5pp alpha</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="M66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S66" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T66" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 9→9 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="U66" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-8.4% ≤ -8% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="W66" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X66" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="Y66" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z66" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA66" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB66" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC66" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD66" s="3" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="AE66" s="3" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="AF66" s="3" t="n">
+        <v>88.19</v>
+      </c>
+      <c r="AG66" s="3" t="n">
+        <v>89.97</v>
+      </c>
+      <c r="AH66" s="3" t="n">
+        <v>84.63</v>
+      </c>
+      <c r="AI66" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ66" s="3" t="n">
+        <v>96.20999999999999</v>
+      </c>
+      <c r="AK66" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL66" s="3" t="n">
+        <v>102.44</v>
+      </c>
+      <c r="AM66" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN66" s="3" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="AO66" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AP66" s="3" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="AQ66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR66" s="3" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="AS66" s="3" t="inlineStr">
+        <is>
+          <t>Momentum · News · Quality</t>
+        </is>
+      </c>
+      <c r="AT66" s="3" t="inlineStr"/>
+      <c r="AU66" s="3" t="inlineStr"/>
+      <c r="AV66" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>MMM_USA_20260730</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +16.4pp alpha</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S67" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T67" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="U67" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-9.2% ≤ -8% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="V67" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="W67" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X67" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="Y67" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z67" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA67" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB67" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AC67" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD67" s="3" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="AE67" s="3" t="n">
+        <v>176.07</v>
+      </c>
+      <c r="AF67" s="3" t="n">
+        <v>174.31</v>
+      </c>
+      <c r="AG67" s="3" t="n">
+        <v>177.83</v>
+      </c>
+      <c r="AH67" s="3" t="n">
+        <v>167.27</v>
+      </c>
+      <c r="AI67" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ67" s="3" t="n">
+        <v>190.16</v>
+      </c>
+      <c r="AK67" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL67" s="3" t="n">
+        <v>202.48</v>
+      </c>
+      <c r="AM67" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN67" s="3" t="n">
+        <v>181.45</v>
+      </c>
+      <c r="AO67" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AP67" s="3" t="n">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="AQ67" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AR67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS67" s="3" t="inlineStr">
+        <is>
+          <t>Momentum · News · Value</t>
+        </is>
+      </c>
+      <c r="AT67" s="3" t="inlineStr"/>
+      <c r="AU67" s="3" t="inlineStr"/>
+      <c r="AV67" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="AW67" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>INTC_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +37.2pp alpha</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="M68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S68" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 26 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T68" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 11→11 · Conf 29% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="U68" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·RAPID_APPRECIATION·+16.1% ≥ +12% · take profit</t>
+        </is>
+      </c>
+      <c r="V68" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X68" s="3" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="Y68" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z68" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA68" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB68" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC68" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD68" s="3" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="AE68" s="3" t="n">
+        <v>81.88</v>
+      </c>
+      <c r="AF68" s="3" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="AG68" s="3" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="AH68" s="3" t="n">
+        <v>77.79000000000001</v>
+      </c>
+      <c r="AI68" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ68" s="3" t="n">
+        <v>88.43000000000001</v>
+      </c>
+      <c r="AK68" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL68" s="3" t="n">
+        <v>94.16</v>
+      </c>
+      <c r="AM68" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN68" s="3" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="AO68" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AP68" s="3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="AQ68" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AR68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS68" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
+        </is>
+      </c>
+      <c r="AT68" s="3" t="inlineStr"/>
+      <c r="AU68" s="3" t="inlineStr"/>
+      <c r="AV68" s="3" t="n">
+        <v>37.17</v>
+      </c>
+      <c r="AW68" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>BA_USA_20260730</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +37.8pp alpha</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>-3.11</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S69" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T69" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 12→12 · Conf 31% · band EXIT · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="U69" s="3" t="inlineStr"/>
+      <c r="V69" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="W69" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X69" s="3" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="Y69" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z69" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA69" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB69" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="AC69" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD69" s="3" t="n">
+        <v>214.03</v>
+      </c>
+      <c r="AE69" s="3" t="n">
+        <v>220.9</v>
+      </c>
+      <c r="AF69" s="3" t="n">
+        <v>218.69</v>
+      </c>
+      <c r="AG69" s="3" t="n">
+        <v>223.11</v>
+      </c>
+      <c r="AH69" s="3" t="n">
+        <v>209.85</v>
+      </c>
+      <c r="AI69" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ69" s="3" t="n">
+        <v>238.57</v>
+      </c>
+      <c r="AK69" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL69" s="3" t="n">
+        <v>254.03</v>
+      </c>
+      <c r="AM69" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN69" s="3" t="n">
+        <v>237.16</v>
+      </c>
+      <c r="AO69" s="3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AP69" s="3" t="n">
+        <v>-3.11</v>
+      </c>
+      <c r="AQ69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR69" s="3" t="n">
+        <v>-2.15</v>
+      </c>
+      <c r="AS69" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
+        </is>
+      </c>
+      <c r="AT69" s="3" t="inlineStr"/>
+      <c r="AU69" s="3" t="inlineStr"/>
+      <c r="AV69" s="3" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="AW69" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>HD_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +43.9pp alpha</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="M70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S70" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 13 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T70" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 13→13 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="U70" s="3" t="inlineStr"/>
+      <c r="V70" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="W70" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X70" s="3" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="Y70" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z70" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA70" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB70" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC70" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD70" s="3" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="AE70" s="3" t="n">
+        <v>338.27</v>
+      </c>
+      <c r="AF70" s="3" t="n">
+        <v>334.89</v>
+      </c>
+      <c r="AG70" s="3" t="n">
+        <v>341.65</v>
+      </c>
+      <c r="AH70" s="3" t="n">
+        <v>321.36</v>
+      </c>
+      <c r="AI70" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ70" s="3" t="n">
+        <v>365.33</v>
+      </c>
+      <c r="AK70" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL70" s="3" t="n">
+        <v>389.01</v>
+      </c>
+      <c r="AM70" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN70" s="3" t="n">
+        <v>348.24</v>
+      </c>
+      <c r="AO70" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AP70" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AQ70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR70" s="3" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="AS70" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AT70" s="3" t="inlineStr"/>
+      <c r="AU70" s="3" t="inlineStr"/>
+      <c r="AV70" s="3" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="AW70" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>DIS_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Walt Disney</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +45.6pp alpha</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="M71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S71" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 19 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T71" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 14→14 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="U71" s="3" t="inlineStr"/>
+      <c r="V71" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="W71" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X71" s="3" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="Y71" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z71" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA71" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB71" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC71" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD71" s="3" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="AE71" s="3" t="n">
+        <v>98.48</v>
+      </c>
+      <c r="AF71" s="3" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="AG71" s="3" t="n">
+        <v>99.45999999999999</v>
+      </c>
+      <c r="AH71" s="3" t="n">
+        <v>93.56</v>
+      </c>
+      <c r="AI71" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ71" s="3" t="n">
+        <v>106.36</v>
+      </c>
+      <c r="AK71" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL71" s="3" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="AM71" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN71" s="3" t="n">
+        <v>98.18000000000001</v>
+      </c>
+      <c r="AO71" s="3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AP71" s="3" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="AQ71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR71" s="3" t="n">
+        <v>-2.36</v>
+      </c>
+      <c r="AS71" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AT71" s="3" t="inlineStr"/>
+      <c r="AU71" s="3" t="inlineStr"/>
+      <c r="AV71" s="3" t="n">
+        <v>45.62</v>
+      </c>
+      <c r="AW71" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>MCD_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>McDonald's</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>→ TRV · +45.9pp alpha</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S72" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 6 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T72" s="3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 15→15 · Conf 28% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="U72" s="3" t="inlineStr"/>
+      <c r="V72" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="W72" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X72" s="3" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="Y72" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z72" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA72" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB72" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC72" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD72" s="3" t="n">
+        <v>267.71</v>
+      </c>
+      <c r="AE72" s="3" t="n">
+        <v>271.52</v>
+      </c>
+      <c r="AF72" s="3" t="n">
+        <v>268.8</v>
+      </c>
+      <c r="AG72" s="3" t="n">
+        <v>274.24</v>
+      </c>
+      <c r="AH72" s="3" t="n">
+        <v>257.94</v>
+      </c>
+      <c r="AI72" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ72" s="3" t="n">
+        <v>293.24</v>
+      </c>
+      <c r="AK72" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL72" s="3" t="n">
+        <v>312.25</v>
+      </c>
+      <c r="AM72" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN72" s="3" t="n">
+        <v>268.34</v>
+      </c>
+      <c r="AO72" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AP72" s="3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AQ72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR72" s="3" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="AS72" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AT72" s="3" t="inlineStr"/>
+      <c r="AU72" s="3" t="inlineStr"/>
+      <c r="AV72" s="3" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="AW72" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>V_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr"/>
+      <c r="K73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" s="3" t="inlineStr"/>
+      <c r="M73" s="3" t="inlineStr"/>
+      <c r="N73" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S73" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T73" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 54% · momentum → · band STRONG · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U73" s="3" t="inlineStr"/>
+      <c r="V73" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="W73" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X73" s="3" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="Y73" s="3" t="inlineStr"/>
+      <c r="Z73" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA73" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB73" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AC73" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD73" s="3" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="AE73" s="3" t="n">
+        <v>368.73</v>
+      </c>
+      <c r="AF73" s="3" t="n">
+        <v>351.39</v>
+      </c>
+      <c r="AG73" s="3" t="n">
+        <v>365.73</v>
+      </c>
+      <c r="AH73" s="3" t="n">
+        <v>340.632</v>
+      </c>
+      <c r="AI73" s="3" t="n">
+        <v>-7.62</v>
+      </c>
+      <c r="AJ73" s="3" t="n">
+        <v>387.2448000000001</v>
+      </c>
+      <c r="AK73" s="3" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="AL73" s="3" t="n">
+        <v>414.3519360000001</v>
+      </c>
+      <c r="AM73" s="3" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="AN73" s="3" t="n">
+        <v>369.59</v>
+      </c>
+      <c r="AO73" s="3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AP73" s="3" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="AQ73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR73" s="3" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="AS73" s="3" t="inlineStr"/>
+      <c r="AT73" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU73" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV73" s="3" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="AW73" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>TRV_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr"/>
+      <c r="K74" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L74" s="3" t="inlineStr"/>
+      <c r="M74" s="3" t="inlineStr"/>
+      <c r="N74" s="3" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q74" s="3" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S74" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T74" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U74" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.2% ≤ -5% · exit</t>
+        </is>
+      </c>
+      <c r="V74" s="3" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="W74" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X74" s="3" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="Y74" s="3" t="inlineStr"/>
+      <c r="Z74" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA74" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB74" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AC74" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD74" s="3" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="AE74" s="3" t="n">
+        <v>389.01</v>
+      </c>
+      <c r="AF74" s="3" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="AG74" s="3" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="AH74" s="3" t="n">
+        <v>350.531</v>
+      </c>
+      <c r="AI74" s="3" t="n">
+        <v>-9.890000000000001</v>
+      </c>
+      <c r="AJ74" s="3" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AK74" s="3" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="AL74" s="3" t="n">
+        <v>442.1882</v>
+      </c>
+      <c r="AM74" s="3" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="AN74" s="3" t="n">
+        <v>377.15</v>
+      </c>
+      <c r="AO74" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AP74" s="3" t="n">
+        <v>-5.15</v>
+      </c>
+      <c r="AQ74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR74" s="3" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="AS74" s="3" t="inlineStr"/>
+      <c r="AT74" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU74" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV74" s="3" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="AW74" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>NVDA_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+      <c r="K75" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L75" s="3" t="inlineStr"/>
+      <c r="M75" s="3" t="inlineStr"/>
+      <c r="N75" s="3" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q75" s="3" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S75" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T75" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 47% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U75" s="3" t="inlineStr"/>
+      <c r="V75" s="3" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="W75" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X75" s="3" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="Y75" s="3" t="inlineStr"/>
+      <c r="Z75" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA75" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB75" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AC75" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD75" s="3" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="AE75" s="3" t="n">
+        <v>190.01</v>
+      </c>
+      <c r="AF75" s="3" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="AG75" s="3" t="n">
+        <v>206.87</v>
+      </c>
+      <c r="AH75" s="3" t="n">
+        <v>192.6695</v>
+      </c>
+      <c r="AI75" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ75" s="3" t="n">
+        <v>219.0348</v>
+      </c>
+      <c r="AK75" s="3" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="AL75" s="3" t="n">
+        <v>234.367236</v>
+      </c>
+      <c r="AM75" s="3" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="AN75" s="3" t="n">
+        <v>211.94</v>
+      </c>
+      <c r="AO75" s="3" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AP75" s="3" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="AQ75" s="3" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AR75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS75" s="3" t="inlineStr"/>
+      <c r="AT75" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU75" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV75" s="3" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="AW75" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>MSFT_USA_20260730</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr"/>
+      <c r="K76" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L76" s="3" t="inlineStr"/>
+      <c r="M76" s="3" t="inlineStr"/>
+      <c r="N76" s="3" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q76" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S76" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T76" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="U76" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-12.7% ≤ -8% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="W76" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Y76" s="3" t="inlineStr"/>
+      <c r="Z76" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA76" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB76" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AC76" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD76" s="3" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="AE76" s="3" t="n">
+        <v>451.1</v>
+      </c>
+      <c r="AF76" s="3" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="AG76" s="3" t="n">
+        <v>401.7</v>
+      </c>
+      <c r="AH76" s="3" t="n">
+        <v>374.129</v>
+      </c>
+      <c r="AI76" s="3" t="n">
+        <v>-17.06</v>
+      </c>
+      <c r="AJ76" s="3" t="n">
+        <v>425.3256</v>
+      </c>
+      <c r="AK76" s="3" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="AL76" s="3" t="n">
+        <v>455.098392</v>
+      </c>
+      <c r="AM76" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AN76" s="3" t="n">
+        <v>492.81</v>
+      </c>
+      <c r="AO76" s="3" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AP76" s="3" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="AQ76" s="3" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AR76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS76" s="3" t="inlineStr"/>
+      <c r="AT76" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU76" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV76" s="3" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="AW76" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>KO_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L77" s="3" t="inlineStr"/>
+      <c r="M77" s="3" t="inlineStr"/>
+      <c r="N77" s="3" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="O77" s="3" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q77" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S77" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T77" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U77" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-8.4% ≤ -8% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="V77" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="W77" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X77" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="Y77" s="3" t="inlineStr"/>
+      <c r="Z77" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA77" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB77" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AC77" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD77" s="3" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="AE77" s="3" t="n">
+        <v>89.08</v>
+      </c>
+      <c r="AF77" s="3" t="n">
+        <v>79.93000000000001</v>
+      </c>
+      <c r="AG77" s="3" t="n">
+        <v>83.19</v>
+      </c>
+      <c r="AH77" s="3" t="n">
+        <v>77.482</v>
+      </c>
+      <c r="AI77" s="3" t="n">
+        <v>-13.02</v>
+      </c>
+      <c r="AJ77" s="3" t="n">
+        <v>88.0848</v>
+      </c>
+      <c r="AK77" s="3" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="AL77" s="3" t="n">
+        <v>94.250736</v>
+      </c>
+      <c r="AM77" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AN77" s="3" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="AO77" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AP77" s="3" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="AQ77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR77" s="3" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="AS77" s="3" t="inlineStr"/>
+      <c r="AT77" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU77" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV77" s="3" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="AW77" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>HON_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L78" s="3" t="inlineStr"/>
+      <c r="M78" s="3" t="inlineStr"/>
+      <c r="N78" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="O78" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q78" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S78" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T78" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U78" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.7% ≤ -5% · exit</t>
+        </is>
+      </c>
+      <c r="V78" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="W78" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X78" s="3" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="Y78" s="3" t="inlineStr"/>
+      <c r="Z78" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA78" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB78" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AC78" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD78" s="3" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="AE78" s="3" t="n">
+        <v>241.12</v>
+      </c>
+      <c r="AF78" s="3" t="n">
+        <v>220.52</v>
+      </c>
+      <c r="AG78" s="3" t="n">
+        <v>229.52</v>
+      </c>
+      <c r="AH78" s="3" t="n">
+        <v>213.769</v>
+      </c>
+      <c r="AI78" s="3" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="AJ78" s="3" t="n">
+        <v>243.0216</v>
+      </c>
+      <c r="AK78" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AL78" s="3" t="n">
+        <v>260.0331120000001</v>
+      </c>
+      <c r="AM78" s="3" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="AN78" s="3" t="n">
+        <v>248.79</v>
+      </c>
+      <c r="AO78" s="3" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AP78" s="3" t="n">
+        <v>-6.68</v>
+      </c>
+      <c r="AQ78" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AR78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS78" s="3" t="inlineStr"/>
+      <c r="AT78" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU78" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV78" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AW78" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>AAPL_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr"/>
+      <c r="J79" s="3" t="inlineStr"/>
+      <c r="K79" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="L79" s="3" t="inlineStr"/>
+      <c r="M79" s="3" t="inlineStr"/>
+      <c r="N79" s="3" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="O79" s="3" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q79" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S79" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T79" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U79" s="3" t="inlineStr"/>
+      <c r="V79" s="3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="W79" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X79" s="3" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="Y79" s="3" t="inlineStr"/>
+      <c r="Z79" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA79" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB79" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AC79" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD79" s="3" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="AE79" s="3" t="n">
+        <v>338.19</v>
+      </c>
+      <c r="AF79" s="3" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="AG79" s="3" t="n">
+        <v>340.41</v>
+      </c>
+      <c r="AH79" s="3" t="n">
+        <v>317.053</v>
+      </c>
+      <c r="AI79" s="3" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="AJ79" s="3" t="n">
+        <v>360.4392</v>
+      </c>
+      <c r="AK79" s="3" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="AL79" s="3" t="n">
+        <v>385.669944</v>
+      </c>
+      <c r="AM79" s="3" t="n">
+        <v>14.04</v>
+      </c>
+      <c r="AN79" s="3" t="n">
+        <v>309.38</v>
+      </c>
+      <c r="AO79" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AP79" s="3" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="AQ79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR79" s="3" t="n">
+        <v>-8.66</v>
+      </c>
+      <c r="AS79" s="3" t="inlineStr"/>
+      <c r="AT79" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU79" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV79" s="3" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="AW79" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>JPM_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="3" t="inlineStr"/>
+      <c r="K80" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L80" s="3" t="inlineStr"/>
+      <c r="M80" s="3" t="inlineStr"/>
+      <c r="N80" s="3" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="O80" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S80" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T80" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U80" s="3" t="inlineStr"/>
+      <c r="V80" s="3" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="W80" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X80" s="3" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="Y80" s="3" t="inlineStr"/>
+      <c r="Z80" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA80" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB80" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AC80" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD80" s="3" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="AE80" s="3" t="n">
+        <v>344.71</v>
+      </c>
+      <c r="AF80" s="3" t="n">
+        <v>334.28</v>
+      </c>
+      <c r="AG80" s="3" t="n">
+        <v>347.92</v>
+      </c>
+      <c r="AH80" s="3" t="n">
+        <v>324.045</v>
+      </c>
+      <c r="AI80" s="3" t="n">
+        <v>-5.99</v>
+      </c>
+      <c r="AJ80" s="3" t="n">
+        <v>368.388</v>
+      </c>
+      <c r="AK80" s="3" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="AL80" s="3" t="n">
+        <v>394.1751600000001</v>
+      </c>
+      <c r="AM80" s="3" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="AN80" s="3" t="n">
+        <v>357.52</v>
+      </c>
+      <c r="AO80" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AP80" s="3" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="AQ80" s="3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AR80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS80" s="3" t="inlineStr"/>
+      <c r="AT80" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU80" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV80" s="3" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="AW80" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>GS_USA_20260729</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="inlineStr"/>
+      <c r="K81" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L81" s="3" t="inlineStr"/>
+      <c r="M81" s="3" t="inlineStr"/>
+      <c r="N81" s="3" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="O81" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q81" s="3" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S81" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T81" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U81" s="3" t="inlineStr"/>
+      <c r="V81" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="W81" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X81" s="3" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="Y81" s="3" t="inlineStr"/>
+      <c r="Z81" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA81" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB81" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AC81" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD81" s="3" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="AE81" s="3" t="n">
+        <v>980.75</v>
+      </c>
+      <c r="AF81" s="3" t="n">
+        <v>1043.92</v>
+      </c>
+      <c r="AG81" s="3" t="n">
+        <v>1086.52</v>
+      </c>
+      <c r="AH81" s="3" t="n">
+        <v>1011.959</v>
+      </c>
+      <c r="AI81" s="3" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AJ81" s="3" t="n">
+        <v>1150.4376</v>
+      </c>
+      <c r="AK81" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="AL81" s="3" t="n">
+        <v>1230.968232</v>
+      </c>
+      <c r="AM81" s="3" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="AN81" s="3" t="n">
+        <v>1052.98</v>
+      </c>
+      <c r="AO81" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP81" s="3" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="AQ81" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS81" s="3" t="inlineStr"/>
+      <c r="AT81" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU81" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV81" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="AW81" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>MMM_USA_20260730</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>R1_NEW</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr"/>
+      <c r="K82" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L82" s="3" t="inlineStr"/>
+      <c r="M82" s="3" t="inlineStr"/>
+      <c r="N82" s="3" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="O82" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="Q82" s="3" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="S82" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="T82" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="U82" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-9.2% ≤ -8% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="V82" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="W82" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="X82" s="3" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="Y82" s="3" t="inlineStr"/>
+      <c r="Z82" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA82" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB82" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="AC82" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD82" s="3" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="AE82" s="3" t="n">
+        <v>176.07</v>
+      </c>
+      <c r="AF82" s="3" t="n">
+        <v>156.64</v>
+      </c>
+      <c r="AG82" s="3" t="n">
+        <v>163.04</v>
+      </c>
+      <c r="AH82" s="3" t="n">
+        <v>151.848</v>
+      </c>
+      <c r="AI82" s="3" t="n">
+        <v>-13.76</v>
+      </c>
+      <c r="AJ82" s="3" t="n">
+        <v>172.6272</v>
+      </c>
+      <c r="AK82" s="3" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="AL82" s="3" t="n">
+        <v>184.711104</v>
+      </c>
+      <c r="AM82" s="3" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="AN82" s="3" t="n">
+        <v>181.45</v>
+      </c>
+      <c r="AO82" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AP82" s="3" t="n">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="AQ82" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AR82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS82" s="3" t="inlineStr"/>
+      <c r="AT82" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AU82" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV82" s="3" t="n">
+        <v>-1.96</v>
+      </c>
+      <c r="AW82" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 04:46</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AX57"/>
+  <autoFilter ref="A1:AW82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-08-07.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-07.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+        <bgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,15 +77,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -905,2495 +935,2495 @@
       </c>
       <c r="AW2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07 09:02</t>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>V_USA_20260731</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Visa</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="n">
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="M3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="3" t="n">
+      <c r="M3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5" t="n">
         <v>86.5</v>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>STRONG</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="Q3" s="5" t="n">
         <v>52.9</v>
       </c>
-      <c r="R3" s="3" t="n">
+      <c r="R3" s="5" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>🟢 BUY (Δ-3.0%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
         </is>
       </c>
-      <c r="U3" s="3" t="inlineStr"/>
-      <c r="V3" s="3" t="n">
+      <c r="U3" s="5" t="inlineStr"/>
+      <c r="V3" s="5" t="n">
         <v>53.6</v>
       </c>
-      <c r="W3" s="3" t="inlineStr">
+      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X3" s="3" t="n">
+      <c r="X3" s="5" t="n">
         <v>27.8</v>
       </c>
-      <c r="Y3" s="3" t="n">
+      <c r="Y3" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="Z3" s="3" t="n">
+      <c r="Z3" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AA3" s="3" t="n">
+      <c r="AA3" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="AB3" s="3" t="n">
+      <c r="AB3" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="AC3" s="3" t="inlineStr">
+      <c r="AC3" s="5" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD3" s="3" t="n">
+      <c r="AD3" s="5" t="n">
         <v>358.56</v>
       </c>
-      <c r="AE3" s="3" t="n">
+      <c r="AE3" s="5" t="n">
         <v>366.13</v>
       </c>
-      <c r="AF3" s="3" t="n">
+      <c r="AF3" s="5" t="n">
         <v>362.47</v>
       </c>
-      <c r="AG3" s="3" t="n">
+      <c r="AG3" s="5" t="n">
         <v>369.79</v>
       </c>
-      <c r="AH3" s="3" t="n">
+      <c r="AH3" s="5" t="n">
         <v>347.82</v>
       </c>
-      <c r="AI3" s="3" t="n">
+      <c r="AI3" s="5" t="n">
         <v>-5</v>
       </c>
-      <c r="AJ3" s="3" t="n">
+      <c r="AJ3" s="5" t="n">
         <v>395.42</v>
       </c>
-      <c r="AK3" s="3" t="n">
+      <c r="AK3" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="AL3" s="3" t="n">
+      <c r="AL3" s="5" t="n">
         <v>421.05</v>
       </c>
-      <c r="AM3" s="3" t="n">
+      <c r="AM3" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AN3" s="3" t="n">
+      <c r="AN3" s="5" t="n">
         <v>369.59</v>
       </c>
-      <c r="AO3" s="3" t="n">
+      <c r="AO3" s="5" t="n">
         <v>-0.28</v>
       </c>
-      <c r="AP3" s="3" t="n">
+      <c r="AP3" s="5" t="n">
         <v>-2.07</v>
       </c>
-      <c r="AQ3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AQ3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="5" t="inlineStr">
         <is>
           <t>Momentum · Trend · Quality</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AT3" s="5" t="inlineStr"/>
+      <c r="AU3" s="5" t="inlineStr"/>
+      <c r="AV3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>NVDA_USA_20260731</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>NVIDIA</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>→ TRV · +12.2pp alpha</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="M4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="3" t="n">
+      <c r="M4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="7" t="n">
         <v>67.5</v>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="7" t="n">
         <v>46.6</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T4" s="7" t="inlineStr">
         <is>
           <t>🔴 AVOID · Rank → 3→3 · Conf 47% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="n">
+      <c r="U4" s="7" t="inlineStr"/>
+      <c r="V4" s="7" t="n">
         <v>47.3</v>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="W4" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="X4" s="7" t="n">
         <v>17.1</v>
       </c>
-      <c r="Y4" s="3" t="n">
+      <c r="Y4" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Z4" s="3" t="n">
+      <c r="Z4" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AA4" s="3" t="n">
+      <c r="AA4" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AB4" s="3" t="n">
+      <c r="AB4" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
+      <c r="AC4" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD4" s="3" t="n">
+      <c r="AD4" s="7" t="n">
         <v>202.81</v>
       </c>
-      <c r="AE4" s="3" t="n">
+      <c r="AE4" s="7" t="n">
         <v>200.75</v>
       </c>
-      <c r="AF4" s="3" t="n">
+      <c r="AF4" s="7" t="n">
         <v>198.74</v>
       </c>
-      <c r="AG4" s="3" t="n">
+      <c r="AG4" s="7" t="n">
         <v>202.76</v>
       </c>
-      <c r="AH4" s="3" t="n">
+      <c r="AH4" s="7" t="n">
         <v>190.71</v>
       </c>
-      <c r="AI4" s="3" t="n">
+      <c r="AI4" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AJ4" s="3" t="n">
+      <c r="AJ4" s="7" t="n">
         <v>216.81</v>
       </c>
-      <c r="AK4" s="3" t="n">
+      <c r="AK4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AL4" s="3" t="n">
+      <c r="AL4" s="7" t="n">
         <v>230.86</v>
       </c>
-      <c r="AM4" s="3" t="n">
+      <c r="AM4" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AN4" s="3" t="n">
+      <c r="AN4" s="7" t="n">
         <v>211.94</v>
       </c>
-      <c r="AO4" s="3" t="n">
+      <c r="AO4" s="7" t="n">
         <v>3.43</v>
       </c>
-      <c r="AP4" s="3" t="n">
+      <c r="AP4" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="AQ4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
+      <c r="AQ4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="7" t="inlineStr">
         <is>
           <t>Quality · Growth · Mean Reversion</t>
         </is>
       </c>
-      <c r="AT4" s="3" t="inlineStr"/>
-      <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="3" t="n">
+      <c r="AT4" s="7" t="inlineStr"/>
+      <c r="AU4" s="7" t="inlineStr"/>
+      <c r="AV4" s="7" t="n">
         <v>12.15</v>
       </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW4" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>JPM_USA_20260731</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>JPM</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>JPMorgan Chase</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>→ TRV · +13.0pp alpha</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J5" s="7" t="n">
         <v>-3.04</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="3" t="n">
+      <c r="M5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="7" t="n">
         <v>48.9</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="T5" s="7" t="inlineStr">
         <is>
           <t>🔴 AVOID · Rank → 4→4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="3" t="n">
+      <c r="U5" s="7" t="inlineStr"/>
+      <c r="V5" s="7" t="n">
         <v>49.7</v>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="W5" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X5" s="3" t="n">
+      <c r="X5" s="7" t="n">
         <v>16.3</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Y5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Z5" s="3" t="n">
+      <c r="Z5" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AA5" s="3" t="n">
+      <c r="AA5" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AB5" s="3" t="n">
+      <c r="AB5" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AC5" s="3" t="inlineStr">
+      <c r="AC5" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD5" s="3" t="n">
+      <c r="AD5" s="7" t="n">
         <v>341.1</v>
       </c>
-      <c r="AE5" s="3" t="n">
+      <c r="AE5" s="7" t="n">
         <v>351.79</v>
       </c>
-      <c r="AF5" s="3" t="n">
+      <c r="AF5" s="7" t="n">
         <v>348.27</v>
       </c>
-      <c r="AG5" s="3" t="n">
+      <c r="AG5" s="7" t="n">
         <v>355.31</v>
       </c>
-      <c r="AH5" s="3" t="n">
+      <c r="AH5" s="7" t="n">
         <v>334.2</v>
       </c>
-      <c r="AI5" s="3" t="n">
+      <c r="AI5" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AJ5" s="3" t="n">
+      <c r="AJ5" s="7" t="n">
         <v>379.93</v>
       </c>
-      <c r="AK5" s="3" t="n">
+      <c r="AK5" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AL5" s="3" t="n">
+      <c r="AL5" s="7" t="n">
         <v>404.56</v>
       </c>
-      <c r="AM5" s="3" t="n">
+      <c r="AM5" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AN5" s="3" t="n">
+      <c r="AN5" s="7" t="n">
         <v>357.52</v>
       </c>
-      <c r="AO5" s="3" t="n">
+      <c r="AO5" s="7" t="n">
         <v>0.48</v>
       </c>
-      <c r="AP5" s="3" t="n">
+      <c r="AP5" s="7" t="n">
         <v>-3.04</v>
       </c>
-      <c r="AQ5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="3" t="inlineStr">
+      <c r="AQ5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" s="7" t="inlineStr">
         <is>
           <t>Momentum · Value · Mean Reversion</t>
         </is>
       </c>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="n">
+      <c r="AT5" s="7" t="inlineStr"/>
+      <c r="AU5" s="7" t="inlineStr"/>
+      <c r="AV5" s="7" t="n">
         <v>12.97</v>
       </c>
-      <c r="AW5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW5" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>HON_USA_20260731</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>HON</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>Honeywell</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>→ TRV · +14.4pp alpha</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" s="7" t="n">
         <v>-7.42</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
+      <c r="M6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="O6" s="3" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="7" t="n">
         <v>49.7</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="T6" s="7" t="inlineStr">
         <is>
           <t>🔴 AVOID · Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr">
+      <c r="U6" s="7" t="inlineStr">
         <is>
           <t>WARNING·STOP_LOSS_HIT·-7.4% ≤ -5% · exit</t>
         </is>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="7" t="n">
         <v>50.5</v>
       </c>
-      <c r="W6" s="3" t="inlineStr">
+      <c r="W6" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X6" s="3" t="n">
+      <c r="X6" s="7" t="n">
         <v>14.8</v>
       </c>
-      <c r="Y6" s="3" t="n">
+      <c r="Y6" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Z6" s="3" t="n">
+      <c r="Z6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AA6" s="3" t="n">
+      <c r="AA6" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AB6" s="3" t="n">
+      <c r="AB6" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AC6" s="3" t="inlineStr">
+      <c r="AC6" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD6" s="3" t="n">
+      <c r="AD6" s="7" t="n">
         <v>225.02</v>
       </c>
-      <c r="AE6" s="3" t="n">
+      <c r="AE6" s="7" t="n">
         <v>243.05</v>
       </c>
-      <c r="AF6" s="3" t="n">
+      <c r="AF6" s="7" t="n">
         <v>240.62</v>
       </c>
-      <c r="AG6" s="3" t="n">
+      <c r="AG6" s="7" t="n">
         <v>245.48</v>
       </c>
-      <c r="AH6" s="3" t="n">
+      <c r="AH6" s="7" t="n">
         <v>230.9</v>
       </c>
-      <c r="AI6" s="3" t="n">
+      <c r="AI6" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AJ6" s="3" t="n">
+      <c r="AJ6" s="7" t="n">
         <v>262.49</v>
       </c>
-      <c r="AK6" s="3" t="n">
+      <c r="AK6" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AL6" s="3" t="n">
+      <c r="AL6" s="7" t="n">
         <v>279.51</v>
       </c>
-      <c r="AM6" s="3" t="n">
+      <c r="AM6" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AN6" s="3" t="n">
+      <c r="AN6" s="7" t="n">
         <v>248.79</v>
       </c>
-      <c r="AO6" s="3" t="n">
+      <c r="AO6" s="7" t="n">
         <v>-0.27</v>
       </c>
-      <c r="AP6" s="3" t="n">
+      <c r="AP6" s="7" t="n">
         <v>-7.42</v>
       </c>
-      <c r="AQ6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="3" t="inlineStr">
+      <c r="AQ6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="7" t="inlineStr">
         <is>
           <t>Mean Reversion · Growth · Value</t>
         </is>
       </c>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="n">
+      <c r="AT6" s="7" t="inlineStr"/>
+      <c r="AU6" s="7" t="inlineStr"/>
+      <c r="AV6" s="7" t="n">
         <v>14.45</v>
       </c>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW6" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>GS_USA_20260731</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>Goldman Sachs</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>→ TRV · +14.8pp alpha</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" s="7" t="n">
         <v>4.6</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="M7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="3" t="n">
+      <c r="M7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="7" t="n">
         <v>66.3</v>
       </c>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="7" t="n">
         <v>50.2</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="T7" s="7" t="inlineStr">
         <is>
           <t>🔴 AVOID · Rank → 6→6 · Conf 51% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U7" s="3" t="inlineStr"/>
-      <c r="V7" s="3" t="n">
+      <c r="U7" s="7" t="inlineStr"/>
+      <c r="V7" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="W7" s="3" t="inlineStr">
+      <c r="W7" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X7" s="3" t="n">
+      <c r="X7" s="7" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y7" s="3" t="n">
+      <c r="Y7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Z7" s="3" t="n">
+      <c r="Z7" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AA7" s="3" t="n">
+      <c r="AA7" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AB7" s="3" t="n">
+      <c r="AB7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AC7" s="3" t="inlineStr">
+      <c r="AC7" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD7" s="3" t="n">
+      <c r="AD7" s="7" t="n">
         <v>1065.22</v>
       </c>
-      <c r="AE7" s="3" t="n">
+      <c r="AE7" s="7" t="n">
         <v>1018.38</v>
       </c>
-      <c r="AF7" s="3" t="n">
+      <c r="AF7" s="7" t="n">
         <v>1008.2</v>
       </c>
-      <c r="AG7" s="3" t="n">
+      <c r="AG7" s="7" t="n">
         <v>1028.56</v>
       </c>
-      <c r="AH7" s="3" t="n">
+      <c r="AH7" s="7" t="n">
         <v>967.46</v>
       </c>
-      <c r="AI7" s="3" t="n">
+      <c r="AI7" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AJ7" s="3" t="n">
+      <c r="AJ7" s="7" t="n">
         <v>1099.85</v>
       </c>
-      <c r="AK7" s="3" t="n">
+      <c r="AK7" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AL7" s="3" t="n">
+      <c r="AL7" s="7" t="n">
         <v>1171.14</v>
       </c>
-      <c r="AM7" s="3" t="n">
+      <c r="AM7" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AN7" s="3" t="n">
+      <c r="AN7" s="7" t="n">
         <v>1052.98</v>
       </c>
-      <c r="AO7" s="3" t="n">
+      <c r="AO7" s="7" t="n">
         <v>0.7</v>
       </c>
-      <c r="AP7" s="3" t="n">
+      <c r="AP7" s="7" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ7" s="3" t="n">
+      <c r="AQ7" s="7" t="n">
         <v>0.64</v>
       </c>
-      <c r="AR7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" s="3" t="inlineStr">
+      <c r="AR7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="7" t="inlineStr">
         <is>
           <t>Value · News · Event Driven</t>
         </is>
       </c>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="n">
+      <c r="AT7" s="7" t="inlineStr"/>
+      <c r="AU7" s="7" t="inlineStr"/>
+      <c r="AV7" s="7" t="n">
         <v>14.77</v>
       </c>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW7" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>AAPL_USA_20260731</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>→ TRV · +14.9pp alpha</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" s="7" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="M8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3" t="n">
+      <c r="M8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7" t="n">
         <v>83.5</v>
       </c>
-      <c r="O8" s="3" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>STRONG</t>
         </is>
       </c>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="P8" s="7" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="7" t="n">
         <v>49.7</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="T8" s="7" t="inlineStr">
         <is>
           <t>🔴 AVOID · Rank → 7→7 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr"/>
-      <c r="V8" s="3" t="n">
+      <c r="U8" s="7" t="inlineStr"/>
+      <c r="V8" s="7" t="n">
         <v>50.5</v>
       </c>
-      <c r="W8" s="3" t="inlineStr">
+      <c r="W8" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="X8" s="7" t="n">
         <v>14.4</v>
       </c>
-      <c r="Y8" s="3" t="n">
+      <c r="Y8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="Z8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AA8" s="3" t="n">
+      <c r="AA8" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AB8" s="3" t="n">
+      <c r="AB8" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AC8" s="3" t="inlineStr">
+      <c r="AC8" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD8" s="3" t="n">
+      <c r="AD8" s="7" t="n">
         <v>333.74</v>
       </c>
-      <c r="AE8" s="3" t="n">
+      <c r="AE8" s="7" t="n">
         <v>308.91</v>
       </c>
-      <c r="AF8" s="3" t="n">
+      <c r="AF8" s="7" t="n">
         <v>305.82</v>
       </c>
-      <c r="AG8" s="3" t="n">
+      <c r="AG8" s="7" t="n">
         <v>312</v>
       </c>
-      <c r="AH8" s="3" t="n">
+      <c r="AH8" s="7" t="n">
         <v>293.46</v>
       </c>
-      <c r="AI8" s="3" t="n">
+      <c r="AI8" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AJ8" s="3" t="n">
+      <c r="AJ8" s="7" t="n">
         <v>333.62</v>
       </c>
-      <c r="AK8" s="3" t="n">
+      <c r="AK8" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AL8" s="3" t="n">
+      <c r="AL8" s="7" t="n">
         <v>355.25</v>
       </c>
-      <c r="AM8" s="3" t="n">
+      <c r="AM8" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AN8" s="3" t="n">
+      <c r="AN8" s="7" t="n">
         <v>309.38</v>
       </c>
-      <c r="AO8" s="3" t="n">
+      <c r="AO8" s="7" t="n">
         <v>0.52</v>
       </c>
-      <c r="AP8" s="3" t="n">
+      <c r="AP8" s="7" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="AQ8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" s="3" t="inlineStr">
+      <c r="AQ8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="7" t="inlineStr">
         <is>
           <t>Value · Trend · Momentum</t>
         </is>
       </c>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="n">
+      <c r="AT8" s="7" t="inlineStr"/>
+      <c r="AU8" s="7" t="inlineStr"/>
+      <c r="AV8" s="7" t="n">
         <v>14.87</v>
       </c>
-      <c r="AW8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW8" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>MSFT_USA_20260731</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>→ TRV · +15.2pp alpha</t>
         </is>
       </c>
-      <c r="J9" s="3" t="n">
+      <c r="J9" s="7" t="n">
         <v>-15.26</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="M9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="n">
+      <c r="M9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="7" t="n">
         <v>79.5</v>
       </c>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="P9" s="7" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="7" t="n">
         <v>52.9</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="T9" s="7" t="inlineStr">
         <is>
           <t>🔴 AVOID · Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="U9" s="7" t="inlineStr">
         <is>
           <t>CRITICAL·DEEP_LOSS·-15.3% ≤ -8% · EXIT URGENT</t>
         </is>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="7" t="n">
         <v>53.6</v>
       </c>
-      <c r="W9" s="3" t="inlineStr">
+      <c r="W9" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X9" s="3" t="n">
+      <c r="X9" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="Y9" s="3" t="n">
+      <c r="Y9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Z9" s="3" t="n">
+      <c r="Z9" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AA9" s="3" t="n">
+      <c r="AA9" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="AB9" s="3" t="n">
+      <c r="AB9" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="AC9" s="3" t="inlineStr">
+      <c r="AC9" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD9" s="3" t="n">
+      <c r="AD9" s="7" t="n">
         <v>393.82</v>
       </c>
-      <c r="AE9" s="3" t="n">
+      <c r="AE9" s="7" t="n">
         <v>464.72</v>
       </c>
-      <c r="AF9" s="3" t="n">
+      <c r="AF9" s="7" t="n">
         <v>460.07</v>
       </c>
-      <c r="AG9" s="3" t="n">
+      <c r="AG9" s="7" t="n">
         <v>469.37</v>
       </c>
-      <c r="AH9" s="3" t="n">
+      <c r="AH9" s="7" t="n">
         <v>441.48</v>
       </c>
-      <c r="AI9" s="3" t="n">
+      <c r="AI9" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AJ9" s="3" t="n">
+      <c r="AJ9" s="7" t="n">
         <v>501.9</v>
       </c>
-      <c r="AK9" s="3" t="n">
+      <c r="AK9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AL9" s="3" t="n">
+      <c r="AL9" s="7" t="n">
         <v>534.4299999999999</v>
       </c>
-      <c r="AM9" s="3" t="n">
+      <c r="AM9" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AN9" s="3" t="n">
+      <c r="AN9" s="7" t="n">
         <v>492.81</v>
       </c>
-      <c r="AO9" s="3" t="n">
+      <c r="AO9" s="7" t="n">
         <v>-1.09</v>
       </c>
-      <c r="AP9" s="3" t="n">
+      <c r="AP9" s="7" t="n">
         <v>-15.26</v>
       </c>
-      <c r="AQ9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" s="3" t="inlineStr">
+      <c r="AQ9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" s="7" t="inlineStr">
         <is>
           <t>Quality · Mean Reversion · Trend</t>
         </is>
       </c>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="n">
+      <c r="AT9" s="7" t="inlineStr"/>
+      <c r="AU9" s="7" t="inlineStr"/>
+      <c r="AV9" s="7" t="n">
         <v>15.21</v>
       </c>
-      <c r="AW9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW9" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>KO_USA_20260731</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>Coca-Cola</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>→ TRV · +15.5pp alpha</t>
         </is>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="J10" s="7" t="n">
         <v>-6.88</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="M10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="n">
+      <c r="M10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="7" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>STRONG</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="7" t="n">
         <v>49.7</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="T10" s="7" t="inlineStr">
         <is>
           <t>🔴 AVOID · Rank → 9→9 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
+      <c r="U10" s="7" t="inlineStr">
         <is>
           <t>WARNING·STOP_LOSS_HIT·-6.9% ≤ -5% · exit</t>
         </is>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="7" t="n">
         <v>50.5</v>
       </c>
-      <c r="W10" s="3" t="inlineStr">
+      <c r="W10" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X10" s="3" t="n">
+      <c r="X10" s="7" t="n">
         <v>13.8</v>
       </c>
-      <c r="Y10" s="3" t="n">
+      <c r="Y10" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Z10" s="3" t="n">
+      <c r="Z10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AA10" s="3" t="n">
+      <c r="AA10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AB10" s="3" t="n">
+      <c r="AB10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AC10" s="3" t="inlineStr">
+      <c r="AC10" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD10" s="3" t="n">
+      <c r="AD10" s="7" t="n">
         <v>81.56</v>
       </c>
-      <c r="AE10" s="3" t="n">
+      <c r="AE10" s="7" t="n">
         <v>87.59</v>
       </c>
-      <c r="AF10" s="3" t="n">
+      <c r="AF10" s="7" t="n">
         <v>86.70999999999999</v>
       </c>
-      <c r="AG10" s="3" t="n">
+      <c r="AG10" s="7" t="n">
         <v>88.47</v>
       </c>
-      <c r="AH10" s="3" t="n">
+      <c r="AH10" s="7" t="n">
         <v>83.20999999999999</v>
       </c>
-      <c r="AI10" s="3" t="n">
+      <c r="AI10" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AJ10" s="3" t="n">
+      <c r="AJ10" s="7" t="n">
         <v>94.59999999999999</v>
       </c>
-      <c r="AK10" s="3" t="n">
+      <c r="AK10" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AL10" s="3" t="n">
+      <c r="AL10" s="7" t="n">
         <v>100.73</v>
       </c>
-      <c r="AM10" s="3" t="n">
+      <c r="AM10" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AN10" s="3" t="n">
+      <c r="AN10" s="7" t="n">
         <v>86.56</v>
       </c>
-      <c r="AO10" s="3" t="n">
+      <c r="AO10" s="7" t="n">
         <v>0.31</v>
       </c>
-      <c r="AP10" s="3" t="n">
+      <c r="AP10" s="7" t="n">
         <v>-6.88</v>
       </c>
-      <c r="AQ10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" s="3" t="inlineStr">
+      <c r="AQ10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="7" t="inlineStr">
         <is>
           <t>Momentum · News · Quality</t>
         </is>
       </c>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="n">
+      <c r="AT10" s="7" t="inlineStr"/>
+      <c r="AU10" s="7" t="inlineStr"/>
+      <c r="AV10" s="7" t="n">
         <v>15.5</v>
       </c>
-      <c r="AW10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW10" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>MMM_USA_20260731</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>MMM</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>→ TRV · +16.4pp alpha</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="J11" s="7" t="n">
         <v>-9.33</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="M11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="3" t="n">
+      <c r="M11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="7" t="n">
         <v>76.2</v>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="P11" s="7" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" s="7" t="n">
         <v>52.9</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="T11" s="7" t="inlineStr">
         <is>
           <t>🔴 AVOID · Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr">
+      <c r="U11" s="7" t="inlineStr">
         <is>
           <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8% · EXIT URGENT</t>
         </is>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="7" t="n">
         <v>53.6</v>
       </c>
-      <c r="W11" s="3" t="inlineStr">
+      <c r="W11" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X11" s="3" t="n">
+      <c r="X11" s="7" t="n">
         <v>12.8</v>
       </c>
-      <c r="Y11" s="3" t="n">
+      <c r="Y11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Z11" s="3" t="n">
+      <c r="Z11" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AA11" s="3" t="n">
+      <c r="AA11" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="AB11" s="3" t="n">
+      <c r="AB11" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="AC11" s="3" t="inlineStr">
+      <c r="AC11" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD11" s="3" t="n">
+      <c r="AD11" s="7" t="n">
         <v>159.84</v>
       </c>
-      <c r="AE11" s="3" t="n">
+      <c r="AE11" s="7" t="n">
         <v>176.28</v>
       </c>
-      <c r="AF11" s="3" t="n">
+      <c r="AF11" s="7" t="n">
         <v>174.52</v>
       </c>
-      <c r="AG11" s="3" t="n">
+      <c r="AG11" s="7" t="n">
         <v>178.04</v>
       </c>
-      <c r="AH11" s="3" t="n">
+      <c r="AH11" s="7" t="n">
         <v>167.47</v>
       </c>
-      <c r="AI11" s="3" t="n">
+      <c r="AI11" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AJ11" s="3" t="n">
+      <c r="AJ11" s="7" t="n">
         <v>190.38</v>
       </c>
-      <c r="AK11" s="3" t="n">
+      <c r="AK11" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AL11" s="3" t="n">
+      <c r="AL11" s="7" t="n">
         <v>202.72</v>
       </c>
-      <c r="AM11" s="3" t="n">
+      <c r="AM11" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AN11" s="3" t="n">
+      <c r="AN11" s="7" t="n">
         <v>181.45</v>
       </c>
-      <c r="AO11" s="3" t="n">
+      <c r="AO11" s="7" t="n">
         <v>0.35</v>
       </c>
-      <c r="AP11" s="3" t="n">
+      <c r="AP11" s="7" t="n">
         <v>-9.33</v>
       </c>
-      <c r="AQ11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" s="3" t="inlineStr">
+      <c r="AQ11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" s="7" t="inlineStr">
         <is>
           <t>Momentum · News · Value</t>
         </is>
       </c>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="n">
+      <c r="AT11" s="7" t="inlineStr"/>
+      <c r="AU11" s="7" t="inlineStr"/>
+      <c r="AV11" s="7" t="n">
         <v>16.4</v>
       </c>
-      <c r="AW11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW11" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>INTC_USA_20260731</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>INTC</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Intel</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>→ TRV · +37.2pp alpha</t>
         </is>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="J12" s="7" t="n">
         <v>5.37</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="M12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="3" t="n">
+      <c r="M12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="7" t="n">
         <v>52.5</v>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="P12" s="7" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S12" s="3" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 26 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="T12" s="7" t="inlineStr">
         <is>
           <t>🔴 AVOID · Rank → 11→11 · Conf 29% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="3" t="n">
+      <c r="U12" s="7" t="inlineStr"/>
+      <c r="V12" s="7" t="n">
         <v>28.7</v>
       </c>
-      <c r="W12" s="3" t="inlineStr">
+      <c r="W12" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X12" s="3" t="n">
+      <c r="X12" s="7" t="n">
         <v>-7.9</v>
       </c>
-      <c r="Y12" s="3" t="n">
+      <c r="Y12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Z12" s="3" t="n">
+      <c r="Z12" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AA12" s="3" t="n">
+      <c r="AA12" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AB12" s="3" t="n">
+      <c r="AB12" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AC12" s="3" t="inlineStr">
+      <c r="AC12" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD12" s="3" t="n">
+      <c r="AD12" s="7" t="n">
         <v>95.04000000000001</v>
       </c>
-      <c r="AE12" s="3" t="n">
+      <c r="AE12" s="7" t="n">
         <v>90.2</v>
       </c>
-      <c r="AF12" s="3" t="n">
+      <c r="AF12" s="7" t="n">
         <v>89.3</v>
       </c>
-      <c r="AG12" s="3" t="n">
+      <c r="AG12" s="7" t="n">
         <v>91.09999999999999</v>
       </c>
-      <c r="AH12" s="3" t="n">
+      <c r="AH12" s="7" t="n">
         <v>85.69</v>
       </c>
-      <c r="AI12" s="3" t="n">
+      <c r="AI12" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AJ12" s="3" t="n">
+      <c r="AJ12" s="7" t="n">
         <v>97.42</v>
       </c>
-      <c r="AK12" s="3" t="n">
+      <c r="AK12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AL12" s="3" t="n">
+      <c r="AL12" s="7" t="n">
         <v>103.73</v>
       </c>
-      <c r="AM12" s="3" t="n">
+      <c r="AM12" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AN12" s="3" t="n">
+      <c r="AN12" s="7" t="n">
         <v>100.86</v>
       </c>
-      <c r="AO12" s="3" t="n">
+      <c r="AO12" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="AP12" s="3" t="n">
+      <c r="AP12" s="7" t="n">
         <v>5.37</v>
       </c>
-      <c r="AQ12" s="3" t="n">
+      <c r="AQ12" s="7" t="n">
         <v>1.03</v>
       </c>
-      <c r="AR12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" s="3" t="inlineStr">
+      <c r="AR12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="7" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AT12" s="3" t="inlineStr"/>
-      <c r="AU12" s="3" t="inlineStr"/>
-      <c r="AV12" s="3" t="n">
+      <c r="AT12" s="7" t="inlineStr"/>
+      <c r="AU12" s="7" t="inlineStr"/>
+      <c r="AV12" s="7" t="n">
         <v>37.17</v>
       </c>
-      <c r="AW12" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW12" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>BA_USA_20260731</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>Boeing</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>→ TRV · +37.8pp alpha</t>
         </is>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" s="7" t="n">
         <v>-0.98</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="M13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3" t="n">
+      <c r="M13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="7" t="n">
         <v>52.6</v>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="P13" s="7" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="7" t="n">
         <v>30.1</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S13" s="3" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="T13" s="7" t="inlineStr">
         <is>
           <t>🔴 AVOID · Rank → 12→12 · Conf 31% · band EXIT · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U13" s="3" t="inlineStr"/>
-      <c r="V13" s="3" t="n">
+      <c r="U13" s="7" t="inlineStr"/>
+      <c r="V13" s="7" t="n">
         <v>30.8</v>
       </c>
-      <c r="W13" s="3" t="inlineStr">
+      <c r="W13" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X13" s="3" t="n">
+      <c r="X13" s="7" t="n">
         <v>-8.5</v>
       </c>
-      <c r="Y13" s="3" t="n">
+      <c r="Y13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Z13" s="3" t="n">
+      <c r="Z13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AA13" s="3" t="n">
+      <c r="AA13" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="AB13" s="3" t="n">
+      <c r="AB13" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="AC13" s="3" t="inlineStr">
+      <c r="AC13" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD13" s="3" t="n">
+      <c r="AD13" s="7" t="n">
         <v>214.03</v>
       </c>
-      <c r="AE13" s="3" t="n">
+      <c r="AE13" s="7" t="n">
         <v>216.14</v>
       </c>
-      <c r="AF13" s="3" t="n">
+      <c r="AF13" s="7" t="n">
         <v>213.98</v>
       </c>
-      <c r="AG13" s="3" t="n">
+      <c r="AG13" s="7" t="n">
         <v>218.3</v>
       </c>
-      <c r="AH13" s="3" t="n">
+      <c r="AH13" s="7" t="n">
         <v>205.33</v>
       </c>
-      <c r="AI13" s="3" t="n">
+      <c r="AI13" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AJ13" s="3" t="n">
+      <c r="AJ13" s="7" t="n">
         <v>233.43</v>
       </c>
-      <c r="AK13" s="3" t="n">
+      <c r="AK13" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AL13" s="3" t="n">
+      <c r="AL13" s="7" t="n">
         <v>248.56</v>
       </c>
-      <c r="AM13" s="3" t="n">
+      <c r="AM13" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AN13" s="3" t="n">
+      <c r="AN13" s="7" t="n">
         <v>237.16</v>
       </c>
-      <c r="AO13" s="3" t="n">
+      <c r="AO13" s="7" t="n">
         <v>1.28</v>
       </c>
-      <c r="AP13" s="3" t="n">
+      <c r="AP13" s="7" t="n">
         <v>-0.98</v>
       </c>
-      <c r="AQ13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="3" t="inlineStr">
+      <c r="AQ13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" s="7" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
         </is>
       </c>
-      <c r="AT13" s="3" t="inlineStr"/>
-      <c r="AU13" s="3" t="inlineStr"/>
-      <c r="AV13" s="3" t="n">
+      <c r="AT13" s="7" t="inlineStr"/>
+      <c r="AU13" s="7" t="inlineStr"/>
+      <c r="AV13" s="7" t="n">
         <v>37.79</v>
       </c>
-      <c r="AW13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW13" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>HD_USA_20260731</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>HD</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Home Depot</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>→ TRV · +43.9pp alpha</t>
         </is>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" s="7" t="n">
         <v>2.08</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="n">
+      <c r="M14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="7" t="n">
         <v>52.8</v>
       </c>
-      <c r="O14" s="3" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="P14" s="7" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S14" s="3" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 13 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="T14" s="7" t="inlineStr">
         <is>
           <t>🔴 AVOID · Rank → 13→13 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr"/>
-      <c r="V14" s="3" t="n">
+      <c r="U14" s="7" t="inlineStr"/>
+      <c r="V14" s="7" t="n">
         <v>34.7</v>
       </c>
-      <c r="W14" s="3" t="inlineStr">
+      <c r="W14" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X14" s="3" t="n">
+      <c r="X14" s="7" t="n">
         <v>-14.6</v>
       </c>
-      <c r="Y14" s="3" t="n">
+      <c r="Y14" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Z14" s="3" t="n">
+      <c r="Z14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AA14" s="3" t="n">
+      <c r="AA14" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AB14" s="3" t="n">
+      <c r="AB14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AC14" s="3" t="inlineStr">
+      <c r="AC14" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD14" s="3" t="n">
+      <c r="AD14" s="7" t="n">
         <v>338.87</v>
       </c>
-      <c r="AE14" s="3" t="n">
+      <c r="AE14" s="7" t="n">
         <v>331.96</v>
       </c>
-      <c r="AF14" s="3" t="n">
+      <c r="AF14" s="7" t="n">
         <v>328.64</v>
       </c>
-      <c r="AG14" s="3" t="n">
+      <c r="AG14" s="7" t="n">
         <v>335.28</v>
       </c>
-      <c r="AH14" s="3" t="n">
+      <c r="AH14" s="7" t="n">
         <v>315.36</v>
       </c>
-      <c r="AI14" s="3" t="n">
+      <c r="AI14" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AJ14" s="3" t="n">
+      <c r="AJ14" s="7" t="n">
         <v>358.52</v>
       </c>
-      <c r="AK14" s="3" t="n">
+      <c r="AK14" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AL14" s="3" t="n">
+      <c r="AL14" s="7" t="n">
         <v>381.75</v>
       </c>
-      <c r="AM14" s="3" t="n">
+      <c r="AM14" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AN14" s="3" t="n">
+      <c r="AN14" s="7" t="n">
         <v>348.24</v>
       </c>
-      <c r="AO14" s="3" t="n">
+      <c r="AO14" s="7" t="n">
         <v>1.41</v>
       </c>
-      <c r="AP14" s="3" t="n">
+      <c r="AP14" s="7" t="n">
         <v>2.08</v>
       </c>
-      <c r="AQ14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" s="3" t="inlineStr">
+      <c r="AQ14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="7" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="n">
+      <c r="AT14" s="7" t="inlineStr"/>
+      <c r="AU14" s="7" t="inlineStr"/>
+      <c r="AV14" s="7" t="n">
         <v>43.85</v>
       </c>
-      <c r="AW14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW14" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>DIS_USA_20260731</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>Walt Disney</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>→ TRV · +45.6pp alpha</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="J15" s="7" t="n">
         <v>1.54</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="M15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="n">
+      <c r="M15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="7" t="n">
         <v>52.8</v>
       </c>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="P15" s="3" t="inlineStr">
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S15" s="3" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 19 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="T15" s="7" t="inlineStr">
         <is>
           <t>🔴 AVOID · Rank → 14→14 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U15" s="3" t="inlineStr"/>
-      <c r="V15" s="3" t="n">
+      <c r="U15" s="7" t="inlineStr"/>
+      <c r="V15" s="7" t="n">
         <v>34.7</v>
       </c>
-      <c r="W15" s="3" t="inlineStr">
+      <c r="W15" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X15" s="3" t="n">
+      <c r="X15" s="7" t="n">
         <v>-16.4</v>
       </c>
-      <c r="Y15" s="3" t="n">
+      <c r="Y15" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Z15" s="3" t="n">
+      <c r="Z15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AA15" s="3" t="n">
+      <c r="AA15" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AB15" s="3" t="n">
+      <c r="AB15" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AC15" s="3" t="inlineStr">
+      <c r="AC15" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD15" s="3" t="n">
+      <c r="AD15" s="7" t="n">
         <v>97.67</v>
       </c>
-      <c r="AE15" s="3" t="n">
+      <c r="AE15" s="7" t="n">
         <v>96.19</v>
       </c>
-      <c r="AF15" s="3" t="n">
+      <c r="AF15" s="7" t="n">
         <v>95.23</v>
       </c>
-      <c r="AG15" s="3" t="n">
+      <c r="AG15" s="7" t="n">
         <v>97.15000000000001</v>
       </c>
-      <c r="AH15" s="3" t="n">
+      <c r="AH15" s="7" t="n">
         <v>91.38</v>
       </c>
-      <c r="AI15" s="3" t="n">
+      <c r="AI15" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AJ15" s="3" t="n">
+      <c r="AJ15" s="7" t="n">
         <v>103.89</v>
       </c>
-      <c r="AK15" s="3" t="n">
+      <c r="AK15" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AL15" s="3" t="n">
+      <c r="AL15" s="7" t="n">
         <v>110.62</v>
       </c>
-      <c r="AM15" s="3" t="n">
+      <c r="AM15" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AN15" s="3" t="n">
+      <c r="AN15" s="7" t="n">
         <v>98.18000000000001</v>
       </c>
-      <c r="AO15" s="3" t="n">
+      <c r="AO15" s="7" t="n">
         <v>3.65</v>
       </c>
-      <c r="AP15" s="3" t="n">
+      <c r="AP15" s="7" t="n">
         <v>1.54</v>
       </c>
-      <c r="AQ15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="3" t="n">
+      <c r="AQ15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="7" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AS15" s="3" t="inlineStr">
+      <c r="AS15" s="7" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="n">
+      <c r="AT15" s="7" t="inlineStr"/>
+      <c r="AU15" s="7" t="inlineStr"/>
+      <c r="AV15" s="7" t="n">
         <v>45.62</v>
       </c>
-      <c r="AW15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW15" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>MCD_USA_20260731</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>MCD</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>McDonald's</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>→ TRV · +45.9pp alpha</t>
         </is>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="J16" s="7" t="n">
         <v>-1.08</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="M16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="n">
+      <c r="M16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="7" t="n">
         <v>52.5</v>
       </c>
-      <c r="O16" s="3" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr">
         <is>
           <t>EXIT</t>
         </is>
       </c>
-      <c r="P16" s="3" t="inlineStr">
+      <c r="P16" s="7" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="7" t="n">
         <v>27.6</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="7" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S16" s="3" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 6 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="T16" s="7" t="inlineStr">
         <is>
           <t>🔴 AVOID · Rank → 15→15 · Conf 28% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
-      <c r="U16" s="3" t="inlineStr"/>
-      <c r="V16" s="3" t="n">
+      <c r="U16" s="7" t="inlineStr"/>
+      <c r="V16" s="7" t="n">
         <v>28.3</v>
       </c>
-      <c r="W16" s="3" t="inlineStr">
+      <c r="W16" s="7" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X16" s="3" t="n">
+      <c r="X16" s="7" t="n">
         <v>-16.7</v>
       </c>
-      <c r="Y16" s="3" t="n">
+      <c r="Y16" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Z16" s="3" t="n">
+      <c r="Z16" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AA16" s="3" t="n">
+      <c r="AA16" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AB16" s="3" t="n">
+      <c r="AB16" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AC16" s="3" t="inlineStr">
+      <c r="AC16" s="7" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD16" s="3" t="n">
+      <c r="AD16" s="7" t="n">
         <v>267.71</v>
       </c>
-      <c r="AE16" s="3" t="n">
+      <c r="AE16" s="7" t="n">
         <v>270.64</v>
       </c>
-      <c r="AF16" s="3" t="n">
+      <c r="AF16" s="7" t="n">
         <v>267.93</v>
       </c>
-      <c r="AG16" s="3" t="n">
+      <c r="AG16" s="7" t="n">
         <v>273.35</v>
       </c>
-      <c r="AH16" s="3" t="n">
+      <c r="AH16" s="7" t="n">
         <v>257.11</v>
       </c>
-      <c r="AI16" s="3" t="n">
+      <c r="AI16" s="7" t="n">
         <v>-5</v>
       </c>
-      <c r="AJ16" s="3" t="n">
+      <c r="AJ16" s="7" t="n">
         <v>292.29</v>
       </c>
-      <c r="AK16" s="3" t="n">
+      <c r="AK16" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AL16" s="3" t="n">
+      <c r="AL16" s="7" t="n">
         <v>311.24</v>
       </c>
-      <c r="AM16" s="3" t="n">
+      <c r="AM16" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="AN16" s="3" t="n">
+      <c r="AN16" s="7" t="n">
         <v>268.34</v>
       </c>
-      <c r="AO16" s="3" t="n">
+      <c r="AO16" s="7" t="n">
         <v>2.11</v>
       </c>
-      <c r="AP16" s="3" t="n">
+      <c r="AP16" s="7" t="n">
         <v>-1.08</v>
       </c>
-      <c r="AQ16" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" s="3" t="n">
+      <c r="AQ16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="7" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="AS16" s="3" t="inlineStr">
+      <c r="AS16" s="7" t="inlineStr">
         <is>
           <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
         </is>
       </c>
-      <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="inlineStr"/>
-      <c r="AV16" s="3" t="n">
+      <c r="AT16" s="7" t="inlineStr"/>
+      <c r="AU16" s="7" t="inlineStr"/>
+      <c r="AV16" s="7" t="n">
         <v>45.94</v>
       </c>
-      <c r="AW16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW16" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3590,7 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07 09:02</t>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3757,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07 09:02</t>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3924,7 @@
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07 09:02</t>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
@@ -4065,1021 +4095,1021 @@
       </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07 09:02</t>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>KO_USA_20260731</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>R1_NEW</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Coca-Cola</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="n">
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="n">
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="n">
         <v>84.09999999999999</v>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>STRONG</t>
         </is>
       </c>
-      <c r="P21" s="3" t="inlineStr">
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" s="5" t="n">
         <v>49.7</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="5" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S21" s="3" t="inlineStr">
+      <c r="S21" s="5" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T21" s="3" t="inlineStr">
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U21" s="3" t="inlineStr">
+      <c r="U21" s="5" t="inlineStr">
         <is>
           <t>WARNING·STOP_LOSS_HIT·-6.9% ≤ -5% · exit</t>
         </is>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="5" t="n">
         <v>50.5</v>
       </c>
-      <c r="W21" s="3" t="inlineStr">
+      <c r="W21" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X21" s="3" t="n">
+      <c r="X21" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="Y21" s="3" t="inlineStr"/>
-      <c r="Z21" s="3" t="n">
+      <c r="Y21" s="5" t="inlineStr"/>
+      <c r="Z21" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AA21" s="3" t="n">
+      <c r="AA21" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="AB21" s="3" t="n">
+      <c r="AB21" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="AC21" s="3" t="inlineStr">
+      <c r="AC21" s="5" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD21" s="3" t="n">
+      <c r="AD21" s="5" t="n">
         <v>81.56</v>
       </c>
-      <c r="AE21" s="3" t="n">
+      <c r="AE21" s="5" t="n">
         <v>87.59</v>
       </c>
-      <c r="AF21" s="3" t="n">
+      <c r="AF21" s="5" t="n">
         <v>79.93000000000001</v>
       </c>
-      <c r="AG21" s="3" t="n">
+      <c r="AG21" s="5" t="n">
         <v>83.19</v>
       </c>
-      <c r="AH21" s="3" t="n">
+      <c r="AH21" s="5" t="n">
         <v>77.482</v>
       </c>
-      <c r="AI21" s="3" t="n">
+      <c r="AI21" s="5" t="n">
         <v>-11.54</v>
       </c>
-      <c r="AJ21" s="3" t="n">
+      <c r="AJ21" s="5" t="n">
         <v>88.0848</v>
       </c>
-      <c r="AK21" s="3" t="n">
+      <c r="AK21" s="5" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AL21" s="3" t="n">
+      <c r="AL21" s="5" t="n">
         <v>94.250736</v>
       </c>
-      <c r="AM21" s="3" t="n">
+      <c r="AM21" s="5" t="n">
         <v>7.6</v>
       </c>
-      <c r="AN21" s="3" t="n">
+      <c r="AN21" s="5" t="n">
         <v>86.56</v>
       </c>
-      <c r="AO21" s="3" t="n">
+      <c r="AO21" s="5" t="n">
         <v>0.31</v>
       </c>
-      <c r="AP21" s="3" t="n">
+      <c r="AP21" s="5" t="n">
         <v>-6.88</v>
       </c>
-      <c r="AQ21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" s="3" t="inlineStr"/>
-      <c r="AT21" s="3" t="inlineStr">
+      <c r="AQ21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" s="5" t="inlineStr"/>
+      <c r="AT21" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AU21" s="3" t="n">
+      <c r="AU21" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AV21" s="3" t="n">
+      <c r="AV21" s="5" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AW21" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW21" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>HON_USA_20260731</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>R1_NEW</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>HON</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Honeywell</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="3" t="n">
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="n">
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="O22" s="3" t="inlineStr">
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="P22" s="3" t="inlineStr">
+      <c r="P22" s="5" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="5" t="n">
         <v>49.7</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="5" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S22" s="3" t="inlineStr">
+      <c r="S22" s="5" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T22" s="3" t="inlineStr">
+      <c r="T22" s="5" t="inlineStr">
         <is>
           <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U22" s="3" t="inlineStr">
+      <c r="U22" s="5" t="inlineStr">
         <is>
           <t>WARNING·STOP_LOSS_HIT·-7.4% ≤ -5% · exit</t>
         </is>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="5" t="n">
         <v>50.5</v>
       </c>
-      <c r="W22" s="3" t="inlineStr">
+      <c r="W22" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X22" s="3" t="n">
+      <c r="X22" s="5" t="n">
         <v>46.5</v>
       </c>
-      <c r="Y22" s="3" t="inlineStr"/>
-      <c r="Z22" s="3" t="n">
+      <c r="Y22" s="5" t="inlineStr"/>
+      <c r="Z22" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AA22" s="3" t="n">
+      <c r="AA22" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="AB22" s="3" t="n">
+      <c r="AB22" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="AC22" s="3" t="inlineStr">
+      <c r="AC22" s="5" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD22" s="3" t="n">
+      <c r="AD22" s="5" t="n">
         <v>225.02</v>
       </c>
-      <c r="AE22" s="3" t="n">
+      <c r="AE22" s="5" t="n">
         <v>243.05</v>
       </c>
-      <c r="AF22" s="3" t="n">
+      <c r="AF22" s="5" t="n">
         <v>220.52</v>
       </c>
-      <c r="AG22" s="3" t="n">
+      <c r="AG22" s="5" t="n">
         <v>229.52</v>
       </c>
-      <c r="AH22" s="3" t="n">
+      <c r="AH22" s="5" t="n">
         <v>213.769</v>
       </c>
-      <c r="AI22" s="3" t="n">
+      <c r="AI22" s="5" t="n">
         <v>-12.05</v>
       </c>
-      <c r="AJ22" s="3" t="n">
+      <c r="AJ22" s="5" t="n">
         <v>243.0216</v>
       </c>
-      <c r="AK22" s="3" t="n">
+      <c r="AK22" s="5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AL22" s="3" t="n">
+      <c r="AL22" s="5" t="n">
         <v>260.0331120000001</v>
       </c>
-      <c r="AM22" s="3" t="n">
+      <c r="AM22" s="5" t="n">
         <v>6.99</v>
       </c>
-      <c r="AN22" s="3" t="n">
+      <c r="AN22" s="5" t="n">
         <v>248.79</v>
       </c>
-      <c r="AO22" s="3" t="n">
+      <c r="AO22" s="5" t="n">
         <v>-0.27</v>
       </c>
-      <c r="AP22" s="3" t="n">
+      <c r="AP22" s="5" t="n">
         <v>-7.42</v>
       </c>
-      <c r="AQ22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" s="3" t="inlineStr"/>
-      <c r="AT22" s="3" t="inlineStr">
+      <c r="AQ22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" s="5" t="inlineStr"/>
+      <c r="AT22" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AU22" s="3" t="n">
+      <c r="AU22" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AV22" s="3" t="n">
+      <c r="AV22" s="5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AW22" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW22" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>AAPL_USA_20260731</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>R1_NEW</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr"/>
-      <c r="K23" s="3" t="n">
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="n">
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="n">
         <v>83.5</v>
       </c>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>STRONG</t>
         </is>
       </c>
-      <c r="P23" s="3" t="inlineStr">
+      <c r="P23" s="5" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="5" t="n">
         <v>49.7</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="5" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S23" s="3" t="inlineStr">
+      <c r="S23" s="5" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T23" s="3" t="inlineStr">
+      <c r="T23" s="5" t="inlineStr">
         <is>
           <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U23" s="3" t="inlineStr"/>
-      <c r="V23" s="3" t="n">
+      <c r="U23" s="5" t="inlineStr"/>
+      <c r="V23" s="5" t="n">
         <v>50.5</v>
       </c>
-      <c r="W23" s="3" t="inlineStr">
+      <c r="W23" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X23" s="3" t="n">
+      <c r="X23" s="5" t="n">
         <v>45.8</v>
       </c>
-      <c r="Y23" s="3" t="inlineStr"/>
-      <c r="Z23" s="3" t="n">
+      <c r="Y23" s="5" t="inlineStr"/>
+      <c r="Z23" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AA23" s="3" t="n">
+      <c r="AA23" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="AB23" s="3" t="n">
+      <c r="AB23" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="AC23" s="3" t="inlineStr">
+      <c r="AC23" s="5" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD23" s="3" t="n">
+      <c r="AD23" s="5" t="n">
         <v>333.74</v>
       </c>
-      <c r="AE23" s="3" t="n">
+      <c r="AE23" s="5" t="n">
         <v>308.91</v>
       </c>
-      <c r="AF23" s="3" t="n">
+      <c r="AF23" s="5" t="n">
         <v>327.07</v>
       </c>
-      <c r="AG23" s="3" t="n">
+      <c r="AG23" s="5" t="n">
         <v>340.41</v>
       </c>
-      <c r="AH23" s="3" t="n">
+      <c r="AH23" s="5" t="n">
         <v>317.053</v>
       </c>
-      <c r="AI23" s="3" t="n">
+      <c r="AI23" s="5" t="n">
         <v>2.64</v>
       </c>
-      <c r="AJ23" s="3" t="n">
+      <c r="AJ23" s="5" t="n">
         <v>360.4392</v>
       </c>
-      <c r="AK23" s="3" t="n">
+      <c r="AK23" s="5" t="n">
         <v>16.68</v>
       </c>
-      <c r="AL23" s="3" t="n">
+      <c r="AL23" s="5" t="n">
         <v>385.669944</v>
       </c>
-      <c r="AM23" s="3" t="n">
+      <c r="AM23" s="5" t="n">
         <v>24.85</v>
       </c>
-      <c r="AN23" s="3" t="n">
+      <c r="AN23" s="5" t="n">
         <v>309.38</v>
       </c>
-      <c r="AO23" s="3" t="n">
+      <c r="AO23" s="5" t="n">
         <v>0.52</v>
       </c>
-      <c r="AP23" s="3" t="n">
+      <c r="AP23" s="5" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="AQ23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" s="3" t="inlineStr"/>
-      <c r="AT23" s="3" t="inlineStr">
+      <c r="AQ23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" s="5" t="inlineStr"/>
+      <c r="AT23" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AU23" s="3" t="n">
+      <c r="AU23" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AV23" s="3" t="n">
+      <c r="AV23" s="5" t="n">
         <v>16.68</v>
       </c>
-      <c r="AW23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW23" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>JPM_USA_20260731</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>R1_NEW</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>JPM</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>JPMorgan Chase</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="n">
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="L24" s="3" t="inlineStr"/>
-      <c r="M24" s="3" t="inlineStr"/>
-      <c r="N24" s="3" t="n">
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="O24" s="3" t="inlineStr">
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="P24" s="3" t="inlineStr">
+      <c r="P24" s="5" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="5" t="n">
         <v>48.9</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="5" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S24" s="3" t="inlineStr">
+      <c r="S24" s="5" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T24" s="3" t="inlineStr">
+      <c r="T24" s="5" t="inlineStr">
         <is>
           <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U24" s="3" t="inlineStr"/>
-      <c r="V24" s="3" t="n">
+      <c r="U24" s="5" t="inlineStr"/>
+      <c r="V24" s="5" t="n">
         <v>49.7</v>
       </c>
-      <c r="W24" s="3" t="inlineStr">
+      <c r="W24" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X24" s="3" t="n">
+      <c r="X24" s="5" t="n">
         <v>37.6</v>
       </c>
-      <c r="Y24" s="3" t="inlineStr"/>
-      <c r="Z24" s="3" t="n">
+      <c r="Y24" s="5" t="inlineStr"/>
+      <c r="Z24" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AA24" s="3" t="n">
+      <c r="AA24" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="AB24" s="3" t="n">
+      <c r="AB24" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="AC24" s="3" t="inlineStr">
+      <c r="AC24" s="5" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD24" s="3" t="n">
+      <c r="AD24" s="5" t="n">
         <v>341.1</v>
       </c>
-      <c r="AE24" s="3" t="n">
+      <c r="AE24" s="5" t="n">
         <v>351.79</v>
       </c>
-      <c r="AF24" s="3" t="n">
+      <c r="AF24" s="5" t="n">
         <v>334.28</v>
       </c>
-      <c r="AG24" s="3" t="n">
+      <c r="AG24" s="5" t="n">
         <v>347.92</v>
       </c>
-      <c r="AH24" s="3" t="n">
+      <c r="AH24" s="5" t="n">
         <v>324.045</v>
       </c>
-      <c r="AI24" s="3" t="n">
+      <c r="AI24" s="5" t="n">
         <v>-7.89</v>
       </c>
-      <c r="AJ24" s="3" t="n">
+      <c r="AJ24" s="5" t="n">
         <v>368.388</v>
       </c>
-      <c r="AK24" s="3" t="n">
+      <c r="AK24" s="5" t="n">
         <v>4.72</v>
       </c>
-      <c r="AL24" s="3" t="n">
+      <c r="AL24" s="5" t="n">
         <v>394.1751600000001</v>
       </c>
-      <c r="AM24" s="3" t="n">
+      <c r="AM24" s="5" t="n">
         <v>12.05</v>
       </c>
-      <c r="AN24" s="3" t="n">
+      <c r="AN24" s="5" t="n">
         <v>357.52</v>
       </c>
-      <c r="AO24" s="3" t="n">
+      <c r="AO24" s="5" t="n">
         <v>0.48</v>
       </c>
-      <c r="AP24" s="3" t="n">
+      <c r="AP24" s="5" t="n">
         <v>-3.04</v>
       </c>
-      <c r="AQ24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" s="3" t="inlineStr"/>
-      <c r="AT24" s="3" t="inlineStr">
+      <c r="AQ24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" s="5" t="inlineStr"/>
+      <c r="AT24" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AU24" s="3" t="n">
+      <c r="AU24" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AV24" s="3" t="n">
+      <c r="AV24" s="5" t="n">
         <v>4.72</v>
       </c>
-      <c r="AW24" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW24" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>GS_USA_20260731</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>R1_NEW</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>GS</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Goldman Sachs</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="n">
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="3" t="n">
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="n">
         <v>66.3</v>
       </c>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="P25" s="3" t="inlineStr">
+      <c r="P25" s="5" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q25" s="3" t="n">
+      <c r="Q25" s="5" t="n">
         <v>50.2</v>
       </c>
-      <c r="R25" s="3" t="n">
+      <c r="R25" s="5" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S25" s="3" t="inlineStr">
+      <c r="S25" s="5" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T25" s="3" t="inlineStr">
+      <c r="T25" s="5" t="inlineStr">
         <is>
           <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="n">
+      <c r="U25" s="5" t="inlineStr"/>
+      <c r="V25" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="W25" s="3" t="inlineStr">
+      <c r="W25" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X25" s="3" t="n">
+      <c r="X25" s="5" t="n">
         <v>36.5</v>
       </c>
-      <c r="Y25" s="3" t="inlineStr"/>
-      <c r="Z25" s="3" t="n">
+      <c r="Y25" s="5" t="inlineStr"/>
+      <c r="Z25" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AA25" s="3" t="n">
+      <c r="AA25" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="AB25" s="3" t="n">
+      <c r="AB25" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="AC25" s="3" t="inlineStr">
+      <c r="AC25" s="5" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD25" s="3" t="n">
+      <c r="AD25" s="5" t="n">
         <v>1065.22</v>
       </c>
-      <c r="AE25" s="3" t="n">
+      <c r="AE25" s="5" t="n">
         <v>1018.38</v>
       </c>
-      <c r="AF25" s="3" t="n">
+      <c r="AF25" s="5" t="n">
         <v>1043.92</v>
       </c>
-      <c r="AG25" s="3" t="n">
+      <c r="AG25" s="5" t="n">
         <v>1086.52</v>
       </c>
-      <c r="AH25" s="3" t="n">
+      <c r="AH25" s="5" t="n">
         <v>1011.959</v>
       </c>
-      <c r="AI25" s="3" t="n">
+      <c r="AI25" s="5" t="n">
         <v>-0.63</v>
       </c>
-      <c r="AJ25" s="3" t="n">
+      <c r="AJ25" s="5" t="n">
         <v>1150.4376</v>
       </c>
-      <c r="AK25" s="3" t="n">
+      <c r="AK25" s="5" t="n">
         <v>12.97</v>
       </c>
-      <c r="AL25" s="3" t="n">
+      <c r="AL25" s="5" t="n">
         <v>1230.968232</v>
       </c>
-      <c r="AM25" s="3" t="n">
+      <c r="AM25" s="5" t="n">
         <v>20.88</v>
       </c>
-      <c r="AN25" s="3" t="n">
+      <c r="AN25" s="5" t="n">
         <v>1052.98</v>
       </c>
-      <c r="AO25" s="3" t="n">
+      <c r="AO25" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="AP25" s="3" t="n">
+      <c r="AP25" s="5" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ25" s="3" t="n">
+      <c r="AQ25" s="5" t="n">
         <v>0.64</v>
       </c>
-      <c r="AR25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" s="3" t="inlineStr"/>
-      <c r="AT25" s="3" t="inlineStr">
+      <c r="AR25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" s="5" t="inlineStr"/>
+      <c r="AT25" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AU25" s="3" t="n">
+      <c r="AU25" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AV25" s="3" t="n">
+      <c r="AV25" s="5" t="n">
         <v>12.97</v>
       </c>
-      <c r="AW25" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW25" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>MMM_USA_20260731</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>R1_NEW</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>MMM</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="inlineStr"/>
-      <c r="K26" s="3" t="n">
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="L26" s="3" t="inlineStr"/>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="n">
+      <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="n">
         <v>76.2</v>
       </c>
-      <c r="O26" s="3" t="inlineStr">
+      <c r="O26" s="5" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="P26" s="3" t="inlineStr">
+      <c r="P26" s="5" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="5" t="n">
         <v>52.9</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="5" t="n">
         <v>-0.8</v>
       </c>
-      <c r="S26" s="3" t="inlineStr">
+      <c r="S26" s="5" t="inlineStr">
         <is>
           <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
-      <c r="T26" s="3" t="inlineStr">
+      <c r="T26" s="5" t="inlineStr">
         <is>
           <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U26" s="3" t="inlineStr">
+      <c r="U26" s="5" t="inlineStr">
         <is>
           <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8% · EXIT URGENT</t>
         </is>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="5" t="n">
         <v>53.6</v>
       </c>
-      <c r="W26" s="3" t="inlineStr">
+      <c r="W26" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X26" s="3" t="n">
+      <c r="X26" s="5" t="n">
         <v>32.3</v>
       </c>
-      <c r="Y26" s="3" t="inlineStr"/>
-      <c r="Z26" s="3" t="n">
+      <c r="Y26" s="5" t="inlineStr"/>
+      <c r="Z26" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AA26" s="3" t="n">
+      <c r="AA26" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="AB26" s="3" t="n">
+      <c r="AB26" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="AC26" s="3" t="inlineStr">
+      <c r="AC26" s="5" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="AD26" s="3" t="n">
+      <c r="AD26" s="5" t="n">
         <v>159.84</v>
       </c>
-      <c r="AE26" s="3" t="n">
+      <c r="AE26" s="5" t="n">
         <v>176.28</v>
       </c>
-      <c r="AF26" s="3" t="n">
+      <c r="AF26" s="5" t="n">
         <v>156.64</v>
       </c>
-      <c r="AG26" s="3" t="n">
+      <c r="AG26" s="5" t="n">
         <v>163.04</v>
       </c>
-      <c r="AH26" s="3" t="n">
+      <c r="AH26" s="5" t="n">
         <v>151.848</v>
       </c>
-      <c r="AI26" s="3" t="n">
+      <c r="AI26" s="5" t="n">
         <v>-13.86</v>
       </c>
-      <c r="AJ26" s="3" t="n">
+      <c r="AJ26" s="5" t="n">
         <v>172.6272</v>
       </c>
-      <c r="AK26" s="3" t="n">
+      <c r="AK26" s="5" t="n">
         <v>-2.07</v>
       </c>
-      <c r="AL26" s="3" t="n">
+      <c r="AL26" s="5" t="n">
         <v>184.711104</v>
       </c>
-      <c r="AM26" s="3" t="n">
+      <c r="AM26" s="5" t="n">
         <v>4.78</v>
       </c>
-      <c r="AN26" s="3" t="n">
+      <c r="AN26" s="5" t="n">
         <v>181.45</v>
       </c>
-      <c r="AO26" s="3" t="n">
+      <c r="AO26" s="5" t="n">
         <v>0.35</v>
       </c>
-      <c r="AP26" s="3" t="n">
+      <c r="AP26" s="5" t="n">
         <v>-9.33</v>
       </c>
-      <c r="AQ26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" s="3" t="inlineStr"/>
-      <c r="AT26" s="3" t="inlineStr">
+      <c r="AQ26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" s="5" t="inlineStr"/>
+      <c r="AT26" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AU26" s="3" t="n">
+      <c r="AU26" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AV26" s="3" t="n">
+      <c r="AV26" s="5" t="n">
         <v>-2.07</v>
       </c>
-      <c r="AW26" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:02</t>
+      <c r="AW26" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07 09:37</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_daily_2026-08-07.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AW$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW13"/>
+  <dimension ref="A1:AV13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -463,48 +463,47 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="50" customWidth="1" min="19" max="19"/>
-    <col width="60" customWidth="1" min="20" max="20"/>
-    <col width="44" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="6" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="50" customWidth="1" min="18" max="18"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
+    <col width="44" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="6" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
     <col width="14" customWidth="1" min="29" max="29"/>
-    <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
     <col width="13" customWidth="1" min="32" max="32"/>
-    <col width="13" customWidth="1" min="33" max="33"/>
-    <col width="11" customWidth="1" min="34" max="34"/>
-    <col width="9" customWidth="1" min="35" max="35"/>
-    <col width="11" customWidth="1" min="36" max="36"/>
-    <col width="8" customWidth="1" min="37" max="37"/>
-    <col width="11" customWidth="1" min="38" max="38"/>
-    <col width="8" customWidth="1" min="39" max="39"/>
-    <col width="11" customWidth="1" min="40" max="40"/>
-    <col width="13" customWidth="1" min="41" max="41"/>
-    <col width="15" customWidth="1" min="42" max="42"/>
-    <col width="12" customWidth="1" min="43" max="43"/>
-    <col width="11" customWidth="1" min="44" max="44"/>
-    <col width="32" customWidth="1" min="45" max="45"/>
-    <col width="20" customWidth="1" min="46" max="46"/>
-    <col width="18" customWidth="1" min="47" max="47"/>
-    <col width="17" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="9" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="8" customWidth="1" min="36" max="36"/>
+    <col width="11" customWidth="1" min="37" max="37"/>
+    <col width="8" customWidth="1" min="38" max="38"/>
+    <col width="11" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="40" max="40"/>
+    <col width="15" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="11" customWidth="1" min="43" max="43"/>
+    <col width="32" customWidth="1" min="44" max="44"/>
+    <col width="20" customWidth="1" min="45" max="45"/>
+    <col width="18" customWidth="1" min="46" max="46"/>
+    <col width="17" customWidth="1" min="47" max="47"/>
+    <col width="20" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -545,210 +544,205 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Position Stage</t>
+          <t>Exit Reason</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Exit Reason</t>
+          <t>Exit P&amp;L %</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Exit P&amp;L %</t>
+          <t>Rank</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Prior Rank</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Prior Rank</t>
+          <t>Rank Δ</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Rank Δ</t>
+          <t>Health</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Health</t>
+          <t>Band</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>Risk Meter</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Risk Meter</t>
+          <t>Adj Conf</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Adj Conf</t>
+          <t>Ctx Drag</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Ctx Drag</t>
+          <t>Ctx Reason</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Ctx Reason</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Alerts</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Alerts</t>
+          <t>Confidence %</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Confidence %</t>
+          <t>Conf Type</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Conf Type</t>
+          <t>Model Score</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>Model Score</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Trading Days</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Trading Days</t>
+          <t>Horizon (d)</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Horizon (d)</t>
+          <t>Days Left</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Days Left</t>
+          <t>Recommended</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Recommended</t>
+          <t>Current Price</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Current Price</t>
+          <t>Entry Price</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Entry Price</t>
+          <t>Buy Zone Low</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Buy Zone Low</t>
+          <t>Buy Zone High</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Buy Zone High</t>
+          <t>Stop Loss</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Stop Loss</t>
+          <t>Risk %</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Risk %</t>
+          <t>Target 1</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Target 1</t>
+          <t>T1 %</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>T1 %</t>
+          <t>Target 2</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>Target 2</t>
+          <t>T2 %</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>T2 %</t>
+          <t>Prev Close</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Prev Close</t>
+          <t>Today Move %</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Today Move %</t>
+          <t>Current Perf %</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>Current Perf %</t>
+          <t>Max Gain %</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>Max Gain %</t>
+          <t>Max DD %</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>Max DD %</t>
+          <t>Top Drivers</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>Top Drivers</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Portfolio Weight %</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>Portfolio Weight %</t>
+          <t>Expected Alpha %</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Alpha %</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
@@ -790,140 +784,135 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
+      <c r="H2" s="3" t="inlineStr"/>
       <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="K2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AC2" s="3" t="n">
+        <v>368.98</v>
+      </c>
+      <c r="AD2" s="3" t="n">
+        <v>374.36</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="AF2" s="3" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="AG2" s="3" t="n">
+        <v>346.84</v>
+      </c>
+      <c r="AH2" s="3" t="n">
+        <v>-7.35</v>
+      </c>
+      <c r="AI2" s="3" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AJ2" s="3" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="AK2" s="3" t="n">
+        <v>457.54</v>
+      </c>
+      <c r="AL2" s="3" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="AM2" s="3" t="n">
+        <v>377.15</v>
+      </c>
+      <c r="AN2" s="3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO2" s="3" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="AP2" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="N2" s="3" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr"/>
-      <c r="V2" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="X2" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z2" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA2" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC2" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AD2" s="3" t="n">
-        <v>368.98</v>
-      </c>
-      <c r="AE2" s="3" t="n">
-        <v>374.36</v>
-      </c>
-      <c r="AF2" s="3" t="n">
-        <v>365.29</v>
-      </c>
-      <c r="AG2" s="3" t="n">
-        <v>372.67</v>
-      </c>
-      <c r="AH2" s="3" t="n">
-        <v>346.84</v>
-      </c>
-      <c r="AI2" s="3" t="n">
-        <v>-7.35</v>
-      </c>
-      <c r="AJ2" s="3" t="n">
-        <v>413.26</v>
-      </c>
-      <c r="AK2" s="3" t="n">
-        <v>10.39</v>
-      </c>
-      <c r="AL2" s="3" t="n">
-        <v>457.54</v>
-      </c>
-      <c r="AM2" s="3" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="AN2" s="3" t="n">
-        <v>377.15</v>
-      </c>
-      <c r="AO2" s="3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AP2" s="3" t="n">
-        <v>-1.44</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" s="3" t="inlineStr">
+      <c r="AR2" s="3" t="inlineStr">
         <is>
           <t>Momentum · Value · Trend</t>
         </is>
       </c>
-      <c r="AT2" s="3" t="inlineStr"/>
+      <c r="AS2" s="3" t="inlineStr"/>
+      <c r="AT2" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="AU2" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV2" s="3" t="n">
         <v>10.39</v>
       </c>
-      <c r="AW2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:51</t>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:01</t>
         </is>
       </c>
     </row>
@@ -963,138 +952,133 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
+      <c r="H3" s="5" t="inlineStr"/>
       <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="K3" s="5" t="n">
         <v>2</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="S3" s="5" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.0%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr"/>
+      <c r="U3" s="5" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="V3" s="5" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="X3" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z3" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA3" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB3" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AC3" s="5" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="AD3" s="5" t="n">
+        <v>366.13</v>
+      </c>
+      <c r="AE3" s="5" t="n">
+        <v>362.47</v>
+      </c>
+      <c r="AF3" s="5" t="n">
+        <v>369.79</v>
+      </c>
+      <c r="AG3" s="5" t="n">
+        <v>347.82</v>
+      </c>
+      <c r="AH3" s="5" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI3" s="5" t="n">
+        <v>395.42</v>
+      </c>
+      <c r="AJ3" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK3" s="5" t="n">
+        <v>421.05</v>
+      </c>
+      <c r="AL3" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM3" s="5" t="n">
+        <v>369.59</v>
+      </c>
+      <c r="AN3" s="5" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AO3" s="5" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="AP3" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>STRONG</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="R3" s="5" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="T3" s="5" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="U3" s="5" t="inlineStr"/>
-      <c r="V3" s="5" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="X3" s="5" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="Y3" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z3" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA3" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB3" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC3" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AD3" s="5" t="n">
-        <v>358.56</v>
-      </c>
-      <c r="AE3" s="5" t="n">
-        <v>366.13</v>
-      </c>
-      <c r="AF3" s="5" t="n">
-        <v>362.47</v>
-      </c>
-      <c r="AG3" s="5" t="n">
-        <v>369.79</v>
-      </c>
-      <c r="AH3" s="5" t="n">
-        <v>347.82</v>
-      </c>
-      <c r="AI3" s="5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AJ3" s="5" t="n">
-        <v>395.42</v>
-      </c>
-      <c r="AK3" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AL3" s="5" t="n">
-        <v>421.05</v>
-      </c>
-      <c r="AM3" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN3" s="5" t="n">
-        <v>369.59</v>
-      </c>
-      <c r="AO3" s="5" t="n">
-        <v>-0.28</v>
-      </c>
-      <c r="AP3" s="5" t="n">
-        <v>-2.07</v>
       </c>
       <c r="AQ3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AR3" s="5" t="n">
+      <c r="AR3" s="5" t="inlineStr">
+        <is>
+          <t>Momentum · Trend · Quality</t>
+        </is>
+      </c>
+      <c r="AS3" s="5" t="inlineStr"/>
+      <c r="AT3" s="5" t="inlineStr"/>
+      <c r="AU3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AS3" s="5" t="inlineStr">
-        <is>
-          <t>Momentum · Trend · Quality</t>
-        </is>
-      </c>
-      <c r="AT3" s="5" t="inlineStr"/>
-      <c r="AU3" s="5" t="inlineStr"/>
-      <c r="AV3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:51</t>
+      <c r="AV3" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:01</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1100,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1134,134 +1118,129 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="K4" s="3" t="inlineStr"/>
       <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="n">
+      <c r="M4" s="3" t="n">
         <v>86.5</v>
       </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>STRONG</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
           <t>🟢</t>
         </is>
       </c>
+      <c r="P4" s="3" t="n">
+        <v>52.9</v>
+      </c>
       <c r="Q4" s="3" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="R4" s="3" t="n">
         <v>-0.8</v>
       </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
           <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 54% · momentum → · band STRONG · 91d left · → BUY</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="n">
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="n">
         <v>53.6</v>
       </c>
-      <c r="W4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="W4" s="3" t="n">
         <v>64.3</v>
       </c>
-      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="Z4" s="3" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="AA4" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB4" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AC4" s="3" t="inlineStr">
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
+      <c r="AC4" s="3" t="n">
+        <v>358.56</v>
+      </c>
       <c r="AD4" s="3" t="n">
-        <v>358.56</v>
+        <v>366.13</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>366.13</v>
+        <v>351.39</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>351.39</v>
+        <v>365.73</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>365.73</v>
+        <v>340.632</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>340.632</v>
+        <v>-6.96</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>-6.96</v>
+        <v>387.2448000000001</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>387.2448000000001</v>
+        <v>5.77</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>5.77</v>
+        <v>414.3519360000001</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>414.3519360000001</v>
+        <v>13.17</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>13.17</v>
+        <v>369.59</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>369.59</v>
+        <v>-0.28</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>-0.28</v>
+        <v>-2.07</v>
       </c>
       <c r="AP4" s="3" t="n">
-        <v>-2.07</v>
+        <v>0</v>
       </c>
       <c r="AQ4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr">
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AT4" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU4" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV4" s="3" t="n">
         <v>5.77</v>
       </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:51</t>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:01</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1262,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1301,134 +1280,129 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="n">
+      <c r="M5" s="3" t="n">
         <v>79.3</v>
       </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
           <t>🟢</t>
         </is>
       </c>
+      <c r="P5" s="3" t="n">
+        <v>56.1</v>
+      </c>
       <c r="Q5" s="3" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="R5" s="3" t="n">
         <v>-0.8</v>
       </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
           <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="3" t="n">
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="n">
         <v>56.8</v>
       </c>
-      <c r="W5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X5" s="3" t="n">
+      <c r="W5" s="3" t="n">
         <v>58.8</v>
       </c>
-      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="Z5" s="3" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="AA5" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AC5" s="3" t="inlineStr">
+      <c r="AB5" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
+      <c r="AC5" s="3" t="n">
+        <v>368.98</v>
+      </c>
       <c r="AD5" s="3" t="n">
-        <v>368.98</v>
+        <v>374.36</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>374.36</v>
+        <v>365.29</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>365.29</v>
+        <v>372.67</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>372.67</v>
+        <v>350.531</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>350.531</v>
+        <v>-6.37</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>-6.37</v>
+        <v>413.26</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>413.26</v>
+        <v>10.39</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>10.39</v>
+        <v>442.1882</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>442.1882</v>
+        <v>18.12</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>18.12</v>
+        <v>377.15</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>377.15</v>
+        <v>1.41</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>1.41</v>
+        <v>-1.44</v>
       </c>
       <c r="AP5" s="3" t="n">
-        <v>-1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr">
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AT5" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU5" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV5" s="3" t="n">
         <v>10.39</v>
       </c>
-      <c r="AW5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:51</t>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:01</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1424,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1468,134 +1442,129 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>3</v>
       </c>
+      <c r="K6" s="3" t="inlineStr"/>
       <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="n">
+      <c r="M6" s="3" t="n">
         <v>67.5</v>
       </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
           <t>🟢</t>
         </is>
       </c>
+      <c r="P6" s="3" t="n">
+        <v>46.6</v>
+      </c>
       <c r="Q6" s="3" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="R6" s="3" t="n">
         <v>-0.8</v>
       </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
           <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 47% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
-      <c r="U6" s="3" t="inlineStr"/>
-      <c r="V6" s="3" t="n">
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="n">
         <v>47.3</v>
       </c>
-      <c r="W6" s="3" t="inlineStr">
+      <c r="V6" s="3" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X6" s="3" t="n">
+      <c r="W6" s="3" t="n">
         <v>55.7</v>
       </c>
-      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="Z6" s="3" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="AA6" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB6" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AC6" s="3" t="inlineStr">
+      <c r="AB6" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
+      <c r="AC6" s="3" t="n">
+        <v>202.81</v>
+      </c>
       <c r="AD6" s="3" t="n">
-        <v>202.81</v>
+        <v>200.75</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>200.75</v>
+        <v>198.75</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>198.75</v>
+        <v>206.87</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>206.87</v>
+        <v>192.6695</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>192.6695</v>
+        <v>-4.03</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>-4.03</v>
+        <v>219.0348</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>219.0348</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>9.109999999999999</v>
+        <v>234.367236</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>234.367236</v>
+        <v>16.75</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>16.75</v>
+        <v>211.94</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>211.94</v>
+        <v>3.43</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>3.43</v>
+        <v>1.03</v>
       </c>
       <c r="AP6" s="3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr">
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AT6" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV6" s="3" t="n">
         <v>9.109999999999999</v>
       </c>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:51</t>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:01</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1586,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1635,138 +1604,133 @@
           <t>BUY</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="n">
+      <c r="J7" s="3" t="n">
         <v>4</v>
       </c>
+      <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="n">
+      <c r="M7" s="3" t="n">
         <v>79.5</v>
       </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
           <t>🟢</t>
         </is>
       </c>
+      <c r="P7" s="3" t="n">
+        <v>52.9</v>
+      </c>
       <c r="Q7" s="3" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="R7" s="3" t="n">
         <v>-0.8</v>
       </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
           <t>CRITICAL·DEEP_LOSS·-15.3% ≤ -8% · EXIT URGENT</t>
         </is>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="U7" s="3" t="n">
         <v>53.6</v>
       </c>
-      <c r="W7" s="3" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X7" s="3" t="n">
+      <c r="W7" s="3" t="n">
         <v>51.8</v>
       </c>
-      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr"/>
+      <c r="Y7" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="Z7" s="3" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB7" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="AC7" s="3" t="inlineStr">
+      <c r="AB7" s="3" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
+      <c r="AC7" s="3" t="n">
+        <v>393.82</v>
+      </c>
       <c r="AD7" s="3" t="n">
-        <v>393.82</v>
+        <v>464.72</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>464.72</v>
+        <v>385.94</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>385.94</v>
+        <v>401.7</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>401.7</v>
+        <v>374.129</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>374.129</v>
+        <v>-19.49</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>-19.49</v>
+        <v>425.3256</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>425.3256</v>
+        <v>-8.48</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>-8.48</v>
+        <v>455.098392</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>455.098392</v>
+        <v>-2.07</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>-2.07</v>
+        <v>492.81</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>492.81</v>
+        <v>-1.09</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-1.09</v>
+        <v>-15.26</v>
       </c>
       <c r="AP7" s="3" t="n">
-        <v>-15.26</v>
+        <v>0</v>
       </c>
       <c r="AQ7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr">
+      <c r="AR7" s="3" t="inlineStr"/>
+      <c r="AS7" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AT7" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV7" s="3" t="n">
         <v>-8.48</v>
       </c>
-      <c r="AW7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:51</t>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:01</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1752,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1806,138 +1770,133 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="5" t="n">
+      <c r="J8" s="5" t="n">
         <v>5</v>
       </c>
+      <c r="K8" s="5" t="inlineStr"/>
       <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr"/>
-      <c r="N8" s="5" t="n">
+      <c r="M8" s="5" t="n">
         <v>84.09999999999999</v>
       </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>STRONG</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="inlineStr">
-        <is>
           <t>🟢</t>
         </is>
       </c>
+      <c r="P8" s="5" t="n">
+        <v>49.7</v>
+      </c>
       <c r="Q8" s="5" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="R8" s="5" t="n">
         <v>-0.8</v>
       </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S8" s="5" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T8" s="5" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="U8" s="5" t="inlineStr">
-        <is>
           <t>WARNING·STOP_LOSS_HIT·-6.9% ≤ -5% · exit</t>
         </is>
       </c>
-      <c r="V8" s="5" t="n">
+      <c r="U8" s="5" t="n">
         <v>50.5</v>
       </c>
-      <c r="W8" s="5" t="inlineStr">
+      <c r="V8" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X8" s="5" t="n">
+      <c r="W8" s="5" t="n">
         <v>46.7</v>
       </c>
-      <c r="Y8" s="5" t="inlineStr"/>
+      <c r="X8" s="5" t="inlineStr"/>
+      <c r="Y8" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="Z8" s="5" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="AA8" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB8" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="AC8" s="5" t="inlineStr">
+      <c r="AB8" s="5" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
+      <c r="AC8" s="5" t="n">
+        <v>81.56</v>
+      </c>
       <c r="AD8" s="5" t="n">
-        <v>81.56</v>
+        <v>87.59</v>
       </c>
       <c r="AE8" s="5" t="n">
-        <v>87.59</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="AF8" s="5" t="n">
-        <v>79.93000000000001</v>
+        <v>83.19</v>
       </c>
       <c r="AG8" s="5" t="n">
-        <v>83.19</v>
+        <v>77.482</v>
       </c>
       <c r="AH8" s="5" t="n">
-        <v>77.482</v>
+        <v>-11.54</v>
       </c>
       <c r="AI8" s="5" t="n">
-        <v>-11.54</v>
+        <v>88.0848</v>
       </c>
       <c r="AJ8" s="5" t="n">
-        <v>88.0848</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AK8" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>94.250736</v>
       </c>
       <c r="AL8" s="5" t="n">
-        <v>94.250736</v>
+        <v>7.6</v>
       </c>
       <c r="AM8" s="5" t="n">
-        <v>7.6</v>
+        <v>86.56</v>
       </c>
       <c r="AN8" s="5" t="n">
-        <v>86.56</v>
+        <v>0.31</v>
       </c>
       <c r="AO8" s="5" t="n">
-        <v>0.31</v>
+        <v>-6.88</v>
       </c>
       <c r="AP8" s="5" t="n">
-        <v>-6.88</v>
+        <v>0</v>
       </c>
       <c r="AQ8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AR8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" s="5" t="inlineStr"/>
-      <c r="AT8" s="5" t="inlineStr">
+      <c r="AR8" s="5" t="inlineStr"/>
+      <c r="AS8" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AT8" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="AU8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV8" s="5" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AW8" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:51</t>
+      <c r="AV8" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:01</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1918,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1977,138 +1936,133 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="H9" s="5" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="n">
+      <c r="J9" s="5" t="n">
         <v>6</v>
       </c>
+      <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="n">
+      <c r="M9" s="5" t="n">
         <v>76</v>
       </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
           <t>🟢</t>
         </is>
       </c>
+      <c r="P9" s="5" t="n">
+        <v>49.7</v>
+      </c>
       <c r="Q9" s="5" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="R9" s="5" t="n">
         <v>-0.8</v>
       </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T9" s="5" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="U9" s="5" t="inlineStr">
-        <is>
           <t>WARNING·STOP_LOSS_HIT·-7.4% ≤ -5% · exit</t>
         </is>
       </c>
-      <c r="V9" s="5" t="n">
+      <c r="U9" s="5" t="n">
         <v>50.5</v>
       </c>
-      <c r="W9" s="5" t="inlineStr">
+      <c r="V9" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X9" s="5" t="n">
+      <c r="W9" s="5" t="n">
         <v>46.5</v>
       </c>
-      <c r="Y9" s="5" t="inlineStr"/>
+      <c r="X9" s="5" t="inlineStr"/>
+      <c r="Y9" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="Z9" s="5" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="AA9" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB9" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="AC9" s="5" t="inlineStr">
+      <c r="AB9" s="5" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
+      <c r="AC9" s="5" t="n">
+        <v>225.02</v>
+      </c>
       <c r="AD9" s="5" t="n">
-        <v>225.02</v>
+        <v>243.05</v>
       </c>
       <c r="AE9" s="5" t="n">
-        <v>243.05</v>
+        <v>220.52</v>
       </c>
       <c r="AF9" s="5" t="n">
-        <v>220.52</v>
+        <v>229.52</v>
       </c>
       <c r="AG9" s="5" t="n">
-        <v>229.52</v>
+        <v>213.769</v>
       </c>
       <c r="AH9" s="5" t="n">
-        <v>213.769</v>
+        <v>-12.05</v>
       </c>
       <c r="AI9" s="5" t="n">
-        <v>-12.05</v>
+        <v>243.0216</v>
       </c>
       <c r="AJ9" s="5" t="n">
-        <v>243.0216</v>
+        <v>-0.01</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>-0.01</v>
+        <v>260.0331120000001</v>
       </c>
       <c r="AL9" s="5" t="n">
-        <v>260.0331120000001</v>
+        <v>6.99</v>
       </c>
       <c r="AM9" s="5" t="n">
-        <v>6.99</v>
+        <v>248.79</v>
       </c>
       <c r="AN9" s="5" t="n">
-        <v>248.79</v>
+        <v>-0.27</v>
       </c>
       <c r="AO9" s="5" t="n">
-        <v>-0.27</v>
+        <v>-7.42</v>
       </c>
       <c r="AP9" s="5" t="n">
-        <v>-7.42</v>
+        <v>0</v>
       </c>
       <c r="AQ9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AR9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" s="5" t="inlineStr"/>
-      <c r="AT9" s="5" t="inlineStr">
+      <c r="AR9" s="5" t="inlineStr"/>
+      <c r="AS9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AT9" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="AU9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV9" s="5" t="n">
         <v>-0.01</v>
       </c>
-      <c r="AW9" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:51</t>
+      <c r="AV9" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:01</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2084,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -2148,134 +2102,129 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>7</v>
       </c>
+      <c r="K10" s="5" t="inlineStr"/>
       <c r="L10" s="5" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr"/>
-      <c r="N10" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>83.5</v>
       </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>STRONG</t>
+        </is>
+      </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>STRONG</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="inlineStr">
-        <is>
           <t>🟢</t>
         </is>
       </c>
+      <c r="P10" s="5" t="n">
+        <v>49.7</v>
+      </c>
       <c r="Q10" s="5" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="R10" s="5" t="n">
         <v>-0.8</v>
       </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S10" s="5" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="T10" s="5" t="inlineStr">
-        <is>
           <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U10" s="5" t="inlineStr"/>
-      <c r="V10" s="5" t="n">
+      <c r="T10" s="5" t="inlineStr"/>
+      <c r="U10" s="5" t="n">
         <v>50.5</v>
       </c>
-      <c r="W10" s="5" t="inlineStr">
+      <c r="V10" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X10" s="5" t="n">
+      <c r="W10" s="5" t="n">
         <v>45.8</v>
       </c>
-      <c r="Y10" s="5" t="inlineStr"/>
+      <c r="X10" s="5" t="inlineStr"/>
+      <c r="Y10" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="Z10" s="5" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="AA10" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB10" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="AC10" s="5" t="inlineStr">
+      <c r="AB10" s="5" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
+      <c r="AC10" s="5" t="n">
+        <v>333.74</v>
+      </c>
       <c r="AD10" s="5" t="n">
-        <v>333.74</v>
+        <v>308.91</v>
       </c>
       <c r="AE10" s="5" t="n">
-        <v>308.91</v>
+        <v>327.07</v>
       </c>
       <c r="AF10" s="5" t="n">
-        <v>327.07</v>
+        <v>340.41</v>
       </c>
       <c r="AG10" s="5" t="n">
-        <v>340.41</v>
+        <v>317.053</v>
       </c>
       <c r="AH10" s="5" t="n">
-        <v>317.053</v>
+        <v>2.64</v>
       </c>
       <c r="AI10" s="5" t="n">
-        <v>2.64</v>
+        <v>360.4392</v>
       </c>
       <c r="AJ10" s="5" t="n">
-        <v>360.4392</v>
+        <v>16.68</v>
       </c>
       <c r="AK10" s="5" t="n">
-        <v>16.68</v>
+        <v>385.669944</v>
       </c>
       <c r="AL10" s="5" t="n">
-        <v>385.669944</v>
+        <v>24.85</v>
       </c>
       <c r="AM10" s="5" t="n">
-        <v>24.85</v>
+        <v>309.38</v>
       </c>
       <c r="AN10" s="5" t="n">
-        <v>309.38</v>
+        <v>0.52</v>
       </c>
       <c r="AO10" s="5" t="n">
-        <v>0.52</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="AP10" s="5" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AR10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" s="5" t="inlineStr"/>
-      <c r="AT10" s="5" t="inlineStr">
+      <c r="AR10" s="5" t="inlineStr"/>
+      <c r="AS10" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AT10" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="AU10" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV10" s="5" t="n">
         <v>16.68</v>
       </c>
-      <c r="AW10" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:51</t>
+      <c r="AV10" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:01</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2246,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -2315,134 +2264,129 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="n">
+      <c r="J11" s="5" t="n">
         <v>8</v>
       </c>
+      <c r="K11" s="5" t="inlineStr"/>
       <c r="L11" s="5" t="inlineStr"/>
-      <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="5" t="n">
+      <c r="M11" s="5" t="n">
         <v>78.40000000000001</v>
       </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="inlineStr">
-        <is>
           <t>🟢</t>
         </is>
       </c>
+      <c r="P11" s="5" t="n">
+        <v>48.9</v>
+      </c>
       <c r="Q11" s="5" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="R11" s="5" t="n">
         <v>-0.8</v>
       </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S11" s="5" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="T11" s="5" t="inlineStr">
-        <is>
           <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U11" s="5" t="inlineStr"/>
-      <c r="V11" s="5" t="n">
+      <c r="T11" s="5" t="inlineStr"/>
+      <c r="U11" s="5" t="n">
         <v>49.7</v>
       </c>
-      <c r="W11" s="5" t="inlineStr">
+      <c r="V11" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X11" s="5" t="n">
+      <c r="W11" s="5" t="n">
         <v>37.6</v>
       </c>
-      <c r="Y11" s="5" t="inlineStr"/>
+      <c r="X11" s="5" t="inlineStr"/>
+      <c r="Y11" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="Z11" s="5" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="AA11" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB11" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="AC11" s="5" t="inlineStr">
+      <c r="AB11" s="5" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
+      <c r="AC11" s="5" t="n">
+        <v>341.1</v>
+      </c>
       <c r="AD11" s="5" t="n">
-        <v>341.1</v>
+        <v>351.79</v>
       </c>
       <c r="AE11" s="5" t="n">
-        <v>351.79</v>
+        <v>334.28</v>
       </c>
       <c r="AF11" s="5" t="n">
-        <v>334.28</v>
+        <v>347.92</v>
       </c>
       <c r="AG11" s="5" t="n">
-        <v>347.92</v>
+        <v>324.045</v>
       </c>
       <c r="AH11" s="5" t="n">
-        <v>324.045</v>
+        <v>-7.89</v>
       </c>
       <c r="AI11" s="5" t="n">
-        <v>-7.89</v>
+        <v>368.388</v>
       </c>
       <c r="AJ11" s="5" t="n">
-        <v>368.388</v>
+        <v>4.72</v>
       </c>
       <c r="AK11" s="5" t="n">
-        <v>4.72</v>
+        <v>394.1751600000001</v>
       </c>
       <c r="AL11" s="5" t="n">
-        <v>394.1751600000001</v>
+        <v>12.05</v>
       </c>
       <c r="AM11" s="5" t="n">
-        <v>12.05</v>
+        <v>357.52</v>
       </c>
       <c r="AN11" s="5" t="n">
-        <v>357.52</v>
+        <v>0.48</v>
       </c>
       <c r="AO11" s="5" t="n">
-        <v>0.48</v>
+        <v>-3.04</v>
       </c>
       <c r="AP11" s="5" t="n">
-        <v>-3.04</v>
+        <v>0</v>
       </c>
       <c r="AQ11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AR11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" s="5" t="inlineStr"/>
-      <c r="AT11" s="5" t="inlineStr">
+      <c r="AR11" s="5" t="inlineStr"/>
+      <c r="AS11" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AT11" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="AU11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV11" s="5" t="n">
         <v>4.72</v>
       </c>
-      <c r="AW11" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:51</t>
+      <c r="AV11" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:01</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2408,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -2482,134 +2426,129 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="n">
+      <c r="J12" s="5" t="n">
         <v>9</v>
       </c>
+      <c r="K12" s="5" t="inlineStr"/>
       <c r="L12" s="5" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr"/>
-      <c r="N12" s="5" t="n">
+      <c r="M12" s="5" t="n">
         <v>66.3</v>
       </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P12" s="5" t="inlineStr">
-        <is>
           <t>🟢</t>
         </is>
       </c>
+      <c r="P12" s="5" t="n">
+        <v>50.2</v>
+      </c>
       <c r="Q12" s="5" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="R12" s="5" t="n">
         <v>-0.8</v>
       </c>
+      <c r="R12" s="5" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="T12" s="5" t="inlineStr">
-        <is>
           <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
-      <c r="U12" s="5" t="inlineStr"/>
-      <c r="V12" s="5" t="n">
+      <c r="T12" s="5" t="inlineStr"/>
+      <c r="U12" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="W12" s="5" t="inlineStr">
+      <c r="V12" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X12" s="5" t="n">
+      <c r="W12" s="5" t="n">
         <v>36.5</v>
       </c>
-      <c r="Y12" s="5" t="inlineStr"/>
+      <c r="X12" s="5" t="inlineStr"/>
+      <c r="Y12" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="Z12" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA12" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="AB12" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AC12" s="5" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="AD12" s="5" t="n">
+        <v>1018.38</v>
+      </c>
+      <c r="AE12" s="5" t="n">
+        <v>1043.92</v>
+      </c>
+      <c r="AF12" s="5" t="n">
+        <v>1086.52</v>
+      </c>
+      <c r="AG12" s="5" t="n">
+        <v>1011.959</v>
+      </c>
+      <c r="AH12" s="5" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="AI12" s="5" t="n">
+        <v>1150.4376</v>
+      </c>
+      <c r="AJ12" s="5" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="AK12" s="5" t="n">
+        <v>1230.968232</v>
+      </c>
+      <c r="AL12" s="5" t="n">
+        <v>20.88</v>
+      </c>
+      <c r="AM12" s="5" t="n">
+        <v>1052.98</v>
+      </c>
+      <c r="AN12" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AO12" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AP12" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AQ12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="5" t="inlineStr"/>
+      <c r="AS12" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT12" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AA12" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB12" s="5" t="n">
-        <v>91</v>
-      </c>
-      <c r="AC12" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="AD12" s="5" t="n">
-        <v>1065.22</v>
-      </c>
-      <c r="AE12" s="5" t="n">
-        <v>1018.38</v>
-      </c>
-      <c r="AF12" s="5" t="n">
-        <v>1043.92</v>
-      </c>
-      <c r="AG12" s="5" t="n">
-        <v>1086.52</v>
-      </c>
-      <c r="AH12" s="5" t="n">
-        <v>1011.959</v>
-      </c>
-      <c r="AI12" s="5" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="AJ12" s="5" t="n">
-        <v>1150.4376</v>
-      </c>
-      <c r="AK12" s="5" t="n">
+      <c r="AU12" s="5" t="n">
         <v>12.97</v>
       </c>
-      <c r="AL12" s="5" t="n">
-        <v>1230.968232</v>
-      </c>
-      <c r="AM12" s="5" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="AN12" s="5" t="n">
-        <v>1052.98</v>
-      </c>
-      <c r="AO12" s="5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP12" s="5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ12" s="5" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AR12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" s="5" t="inlineStr"/>
-      <c r="AT12" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU12" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV12" s="5" t="n">
-        <v>12.97</v>
-      </c>
-      <c r="AW12" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:51</t>
+      <c r="AV12" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:01</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2570,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>R1_NEW</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -2649,143 +2588,138 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
+      <c r="H13" s="5" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr"/>
-      <c r="K13" s="5" t="n">
+      <c r="J13" s="5" t="n">
         <v>10</v>
       </c>
+      <c r="K13" s="5" t="inlineStr"/>
       <c r="L13" s="5" t="inlineStr"/>
-      <c r="M13" s="5" t="inlineStr"/>
-      <c r="N13" s="5" t="n">
+      <c r="M13" s="5" t="n">
         <v>76.2</v>
       </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="inlineStr">
-        <is>
           <t>🟢</t>
         </is>
       </c>
+      <c r="P13" s="5" t="n">
+        <v>52.9</v>
+      </c>
       <c r="Q13" s="5" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="R13" s="5" t="n">
         <v>-0.8</v>
       </c>
+      <c r="R13" s="5" t="inlineStr">
+        <is>
+          <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
       <c r="S13" s="5" t="inlineStr">
         <is>
-          <t>crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T13" s="5" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="U13" s="5" t="inlineStr">
-        <is>
           <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8% · EXIT URGENT</t>
         </is>
       </c>
-      <c r="V13" s="5" t="n">
+      <c r="U13" s="5" t="n">
         <v>53.6</v>
       </c>
-      <c r="W13" s="5" t="inlineStr">
+      <c r="V13" s="5" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="X13" s="5" t="n">
+      <c r="W13" s="5" t="n">
         <v>32.3</v>
       </c>
-      <c r="Y13" s="5" t="inlineStr"/>
+      <c r="X13" s="5" t="inlineStr"/>
+      <c r="Y13" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="Z13" s="5" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="AA13" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB13" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="AC13" s="5" t="inlineStr">
+      <c r="AB13" s="5" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
+      <c r="AC13" s="5" t="n">
+        <v>159.84</v>
+      </c>
       <c r="AD13" s="5" t="n">
-        <v>159.84</v>
+        <v>176.28</v>
       </c>
       <c r="AE13" s="5" t="n">
-        <v>176.28</v>
+        <v>156.64</v>
       </c>
       <c r="AF13" s="5" t="n">
-        <v>156.64</v>
+        <v>163.04</v>
       </c>
       <c r="AG13" s="5" t="n">
-        <v>163.04</v>
+        <v>151.848</v>
       </c>
       <c r="AH13" s="5" t="n">
-        <v>151.848</v>
+        <v>-13.86</v>
       </c>
       <c r="AI13" s="5" t="n">
-        <v>-13.86</v>
+        <v>172.6272</v>
       </c>
       <c r="AJ13" s="5" t="n">
-        <v>172.6272</v>
+        <v>-2.07</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>-2.07</v>
+        <v>184.711104</v>
       </c>
       <c r="AL13" s="5" t="n">
-        <v>184.711104</v>
+        <v>4.78</v>
       </c>
       <c r="AM13" s="5" t="n">
-        <v>4.78</v>
+        <v>181.45</v>
       </c>
       <c r="AN13" s="5" t="n">
-        <v>181.45</v>
+        <v>0.35</v>
       </c>
       <c r="AO13" s="5" t="n">
-        <v>0.35</v>
+        <v>-9.33</v>
       </c>
       <c r="AP13" s="5" t="n">
-        <v>-9.33</v>
+        <v>0</v>
       </c>
       <c r="AQ13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AR13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" s="5" t="inlineStr"/>
-      <c r="AT13" s="5" t="inlineStr">
+      <c r="AR13" s="5" t="inlineStr"/>
+      <c r="AS13" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
+      <c r="AT13" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="AU13" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV13" s="5" t="n">
         <v>-2.07</v>
       </c>
-      <c r="AW13" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-07 09:51</t>
+      <c r="AV13" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AW13"/>
+  <autoFilter ref="A1:AV13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>